--- a/tests/testthat/fixtures/example.xlsx
+++ b/tests/testthat/fixtures/example.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -542,229 +542,243 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Advanced settings may be added as extra rows, e.g. cores, thin, adapt_delta,</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  max_treedepth, df, or dose_schedule (the age each dose is given, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Oldest age        oldest age this count covers (for a single age, repeat it or leave blank)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -938,7 +952,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -963,7 +977,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -988,7 +1002,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1013,7 +1027,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1038,7 +1052,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1063,7 +1077,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1088,7 +1102,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1113,7 +1127,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1138,7 +1152,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1163,7 +1177,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1188,7 +1202,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1213,7 +1227,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1238,7 +1252,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1263,7 +1277,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1288,7 +1302,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1313,7 +1327,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -1338,7 +1352,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1363,7 +1377,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -1388,7 +1402,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -1413,7 +1427,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1438,7 +1452,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -1463,7 +1477,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -1488,7 +1502,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -1513,7 +1527,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -1538,7 +1552,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1563,7 +1577,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -1588,7 +1602,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -1613,7 +1627,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1638,7 +1652,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -1663,7 +1677,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -1688,7 +1702,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1713,7 +1727,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -1738,7 +1752,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -1763,7 +1777,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -1788,7 +1802,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -1813,7 +1827,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -1838,7 +1852,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -1863,7 +1877,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -1888,7 +1902,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C40">
         <v>5</v>
@@ -1913,7 +1927,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -1938,7 +1952,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -1963,7 +1977,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -1988,7 +2002,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -2013,7 +2027,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2038,7 +2052,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -2063,7 +2077,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -2088,7 +2102,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -2113,7 +2127,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -2138,7 +2152,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -2163,7 +2177,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C51">
         <v>5</v>
@@ -2188,7 +2202,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -2213,7 +2227,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C53">
         <v>5</v>
@@ -2238,7 +2252,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C54">
         <v>5</v>
@@ -2263,7 +2277,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -2288,7 +2302,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -2313,7 +2327,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C57">
         <v>5</v>
@@ -2338,7 +2352,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C58">
         <v>5</v>
@@ -2363,7 +2377,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -2388,7 +2402,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2413,7 +2427,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C61">
         <v>5</v>
@@ -2438,7 +2452,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2463,7 +2477,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2488,7 +2502,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C64">
         <v>5</v>
@@ -2513,7 +2527,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -2538,7 +2552,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -2563,7 +2577,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C67">
         <v>5</v>
@@ -2588,7 +2602,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C68">
         <v>5</v>
@@ -2613,7 +2627,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C69">
         <v>5</v>
@@ -2638,7 +2652,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C70">
         <v>5</v>
@@ -2663,7 +2677,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C71">
         <v>5</v>
@@ -2688,7 +2702,7 @@
         </is>
       </c>
       <c r="B72">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C72">
         <v>5</v>
@@ -2713,7 +2727,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -2738,7 +2752,7 @@
         </is>
       </c>
       <c r="B74">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -2763,7 +2777,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -2788,7 +2802,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C76">
         <v>5</v>
@@ -2813,7 +2827,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C77">
         <v>5</v>
@@ -2838,7 +2852,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C78">
         <v>5</v>
@@ -2863,7 +2877,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C79">
         <v>5</v>
@@ -2888,7 +2902,7 @@
         </is>
       </c>
       <c r="B80">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C80">
         <v>5</v>
@@ -2913,7 +2927,7 @@
         </is>
       </c>
       <c r="B81">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C81">
         <v>5</v>
@@ -2938,7 +2952,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C82">
         <v>5</v>
@@ -2963,7 +2977,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -2988,7 +3002,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -3013,7 +3027,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C85">
         <v>5</v>
@@ -3038,7 +3052,7 @@
         </is>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C86">
         <v>5</v>
@@ -3063,7 +3077,7 @@
         </is>
       </c>
       <c r="B87">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -3088,7 +3102,7 @@
         </is>
       </c>
       <c r="B88">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C88">
         <v>5</v>
@@ -3113,7 +3127,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C89">
         <v>5</v>
@@ -3138,7 +3152,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C90">
         <v>5</v>
@@ -3163,7 +3177,7 @@
         </is>
       </c>
       <c r="B91">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C91">
         <v>5</v>
@@ -3188,7 +3202,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C92">
         <v>5</v>
@@ -3213,7 +3227,7 @@
         </is>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C93">
         <v>5</v>
@@ -3238,7 +3252,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C94">
         <v>5</v>
@@ -3263,7 +3277,7 @@
         </is>
       </c>
       <c r="B95">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3288,7 +3302,7 @@
         </is>
       </c>
       <c r="B96">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -3313,7 +3327,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C97">
         <v>5</v>
@@ -3338,7 +3352,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C98">
         <v>5</v>
@@ -3363,7 +3377,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -3388,7 +3402,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C100">
         <v>5</v>
@@ -3413,7 +3427,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C101">
         <v>5</v>
@@ -3438,7 +3452,7 @@
         </is>
       </c>
       <c r="B102">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -3463,7 +3477,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C103">
         <v>5</v>
@@ -3488,7 +3502,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C104">
         <v>5</v>
@@ -3513,7 +3527,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C105">
         <v>5</v>
@@ -3538,7 +3552,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C106">
         <v>5</v>
@@ -3563,7 +3577,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C107">
         <v>5</v>
@@ -3588,7 +3602,7 @@
         </is>
       </c>
       <c r="B108">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C108">
         <v>5</v>
@@ -3613,7 +3627,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -3638,7 +3652,7 @@
         </is>
       </c>
       <c r="B110">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C110">
         <v>5</v>
@@ -3663,7 +3677,7 @@
         </is>
       </c>
       <c r="B111">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C111">
         <v>5</v>
@@ -3688,7 +3702,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C112">
         <v>5</v>
@@ -3713,7 +3727,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C113">
         <v>5</v>
@@ -3738,7 +3752,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C114">
         <v>5</v>
@@ -3763,7 +3777,7 @@
         </is>
       </c>
       <c r="B115">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C115">
         <v>5</v>
@@ -3788,7 +3802,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C116">
         <v>5</v>
@@ -3813,7 +3827,7 @@
         </is>
       </c>
       <c r="B117">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C117">
         <v>5</v>
@@ -3838,7 +3852,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C118">
         <v>5</v>
@@ -3863,7 +3877,7 @@
         </is>
       </c>
       <c r="B119">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C119">
         <v>5</v>
@@ -3888,7 +3902,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C120">
         <v>5</v>
@@ -3913,7 +3927,7 @@
         </is>
       </c>
       <c r="B121">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C121">
         <v>5</v>
@@ -3938,7 +3952,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -3963,7 +3977,7 @@
         </is>
       </c>
       <c r="B123">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C123">
         <v>5</v>
@@ -3988,7 +4002,7 @@
         </is>
       </c>
       <c r="B124">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C124">
         <v>5</v>
@@ -4013,7 +4027,7 @@
         </is>
       </c>
       <c r="B125">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C125">
         <v>5</v>
@@ -4038,7 +4052,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C126">
         <v>5</v>
@@ -4063,7 +4077,7 @@
         </is>
       </c>
       <c r="B127">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -4088,7 +4102,7 @@
         </is>
       </c>
       <c r="B128">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C128">
         <v>5</v>
@@ -4113,7 +4127,7 @@
         </is>
       </c>
       <c r="B129">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C129">
         <v>5</v>
@@ -4138,7 +4152,7 @@
         </is>
       </c>
       <c r="B130">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C130">
         <v>5</v>
@@ -4163,7 +4177,7 @@
         </is>
       </c>
       <c r="B131">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C131">
         <v>5</v>
@@ -4188,7 +4202,7 @@
         </is>
       </c>
       <c r="B132">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C132">
         <v>5</v>
@@ -4213,7 +4227,7 @@
         </is>
       </c>
       <c r="B133">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -4238,7 +4252,7 @@
         </is>
       </c>
       <c r="B134">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C134">
         <v>5</v>
@@ -4263,7 +4277,7 @@
         </is>
       </c>
       <c r="B135">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C135">
         <v>5</v>
@@ -4288,7 +4302,7 @@
         </is>
       </c>
       <c r="B136">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C136">
         <v>5</v>
@@ -4313,7 +4327,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C137">
         <v>5</v>
@@ -4338,7 +4352,7 @@
         </is>
       </c>
       <c r="B138">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C138">
         <v>5</v>
@@ -4363,7 +4377,7 @@
         </is>
       </c>
       <c r="B139">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C139">
         <v>5</v>
@@ -4388,7 +4402,7 @@
         </is>
       </c>
       <c r="B140">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C140">
         <v>5</v>
@@ -4413,7 +4427,7 @@
         </is>
       </c>
       <c r="B141">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C141">
         <v>5</v>
@@ -4438,7 +4452,7 @@
         </is>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C142">
         <v>5</v>
@@ -4463,7 +4477,7 @@
         </is>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C143">
         <v>5</v>
@@ -4488,7 +4502,7 @@
         </is>
       </c>
       <c r="B144">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C144">
         <v>5</v>
@@ -4513,7 +4527,7 @@
         </is>
       </c>
       <c r="B145">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C145">
         <v>5</v>
@@ -4538,7 +4552,7 @@
         </is>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C146">
         <v>5</v>
@@ -4563,7 +4577,7 @@
         </is>
       </c>
       <c r="B147">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C147">
         <v>5</v>
@@ -4588,7 +4602,7 @@
         </is>
       </c>
       <c r="B148">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C148">
         <v>5</v>
@@ -4613,7 +4627,7 @@
         </is>
       </c>
       <c r="B149">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C149">
         <v>5</v>
@@ -4638,7 +4652,7 @@
         </is>
       </c>
       <c r="B150">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C150">
         <v>5</v>
@@ -4663,7 +4677,7 @@
         </is>
       </c>
       <c r="B151">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C151">
         <v>5</v>
@@ -4688,7 +4702,7 @@
         </is>
       </c>
       <c r="B152">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C152">
         <v>5</v>
@@ -4713,7 +4727,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C153">
         <v>5</v>
@@ -4738,7 +4752,7 @@
         </is>
       </c>
       <c r="B154">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C154">
         <v>5</v>
@@ -4763,7 +4777,7 @@
         </is>
       </c>
       <c r="B155">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C155">
         <v>5</v>
@@ -4788,7 +4802,7 @@
         </is>
       </c>
       <c r="B156">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C156">
         <v>5</v>
@@ -4813,7 +4827,7 @@
         </is>
       </c>
       <c r="B157">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -4838,7 +4852,7 @@
         </is>
       </c>
       <c r="B158">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C158">
         <v>5</v>
@@ -4863,7 +4877,7 @@
         </is>
       </c>
       <c r="B159">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C159">
         <v>5</v>
@@ -4888,7 +4902,7 @@
         </is>
       </c>
       <c r="B160">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C160">
         <v>5</v>
@@ -4913,7 +4927,7 @@
         </is>
       </c>
       <c r="B161">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -4938,7 +4952,7 @@
         </is>
       </c>
       <c r="B162">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -4963,7 +4977,7 @@
         </is>
       </c>
       <c r="B163">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C163">
         <v>5</v>
@@ -4988,7 +5002,7 @@
         </is>
       </c>
       <c r="B164">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C164">
         <v>5</v>
@@ -5013,7 +5027,7 @@
         </is>
       </c>
       <c r="B165">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C165">
         <v>5</v>
@@ -5038,7 +5052,7 @@
         </is>
       </c>
       <c r="B166">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C166">
         <v>5</v>
@@ -5063,7 +5077,7 @@
         </is>
       </c>
       <c r="B167">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -5088,7 +5102,7 @@
         </is>
       </c>
       <c r="B168">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C168">
         <v>5</v>
@@ -5113,7 +5127,7 @@
         </is>
       </c>
       <c r="B169">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C169">
         <v>5</v>
@@ -5138,7 +5152,7 @@
         </is>
       </c>
       <c r="B170">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C170">
         <v>5</v>
@@ -5163,7 +5177,7 @@
         </is>
       </c>
       <c r="B171">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C171">
         <v>5</v>
@@ -5188,7 +5202,7 @@
         </is>
       </c>
       <c r="B172">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C172">
         <v>5</v>
@@ -5213,7 +5227,7 @@
         </is>
       </c>
       <c r="B173">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C173">
         <v>5</v>
@@ -5238,7 +5252,7 @@
         </is>
       </c>
       <c r="B174">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -5263,7 +5277,7 @@
         </is>
       </c>
       <c r="B175">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -5288,7 +5302,7 @@
         </is>
       </c>
       <c r="B176">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C176">
         <v>5</v>
@@ -5313,7 +5327,7 @@
         </is>
       </c>
       <c r="B177">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -5338,7 +5352,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -5363,7 +5377,7 @@
         </is>
       </c>
       <c r="B179">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -5388,7 +5402,7 @@
         </is>
       </c>
       <c r="B180">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C180">
         <v>5</v>
@@ -5413,7 +5427,7 @@
         </is>
       </c>
       <c r="B181">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C181">
         <v>5</v>
@@ -5438,7 +5452,7 @@
         </is>
       </c>
       <c r="B182">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C182">
         <v>5</v>
@@ -5463,7 +5477,7 @@
         </is>
       </c>
       <c r="B183">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C183">
         <v>5</v>
@@ -5488,7 +5502,7 @@
         </is>
       </c>
       <c r="B184">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C184">
         <v>5</v>
@@ -5513,7 +5527,7 @@
         </is>
       </c>
       <c r="B185">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C185">
         <v>5</v>
@@ -5538,7 +5552,7 @@
         </is>
       </c>
       <c r="B186">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C186">
         <v>5</v>
@@ -5563,7 +5577,7 @@
         </is>
       </c>
       <c r="B187">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C187">
         <v>5</v>
@@ -5588,7 +5602,7 @@
         </is>
       </c>
       <c r="B188">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C188">
         <v>5</v>
@@ -5613,7 +5627,7 @@
         </is>
       </c>
       <c r="B189">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C189">
         <v>5</v>
@@ -5638,7 +5652,7 @@
         </is>
       </c>
       <c r="B190">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C190">
         <v>5</v>
@@ -5663,7 +5677,7 @@
         </is>
       </c>
       <c r="B191">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C191">
         <v>5</v>
@@ -5688,7 +5702,7 @@
         </is>
       </c>
       <c r="B192">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C192">
         <v>5</v>
@@ -5713,7 +5727,7 @@
         </is>
       </c>
       <c r="B193">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C193">
         <v>5</v>
@@ -5738,7 +5752,7 @@
         </is>
       </c>
       <c r="B194">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C194">
         <v>5</v>
@@ -5763,7 +5777,7 @@
         </is>
       </c>
       <c r="B195">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C195">
         <v>5</v>
@@ -5788,7 +5802,7 @@
         </is>
       </c>
       <c r="B196">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C196">
         <v>5</v>
@@ -5813,7 +5827,7 @@
         </is>
       </c>
       <c r="B197">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C197">
         <v>5</v>
@@ -5838,7 +5852,7 @@
         </is>
       </c>
       <c r="B198">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -5863,7 +5877,7 @@
         </is>
       </c>
       <c r="B199">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C199">
         <v>5</v>
@@ -5888,7 +5902,7 @@
         </is>
       </c>
       <c r="B200">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C200">
         <v>5</v>
@@ -5913,7 +5927,7 @@
         </is>
       </c>
       <c r="B201">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C201">
         <v>5</v>
@@ -5938,7 +5952,7 @@
         </is>
       </c>
       <c r="B202">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C202">
         <v>5</v>
@@ -5963,7 +5977,7 @@
         </is>
       </c>
       <c r="B203">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C203">
         <v>5</v>
@@ -5988,7 +6002,7 @@
         </is>
       </c>
       <c r="B204">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -6013,7 +6027,7 @@
         </is>
       </c>
       <c r="B205">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -6038,7 +6052,7 @@
         </is>
       </c>
       <c r="B206">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -6063,7 +6077,7 @@
         </is>
       </c>
       <c r="B207">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -6088,7 +6102,7 @@
         </is>
       </c>
       <c r="B208">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -6113,7 +6127,7 @@
         </is>
       </c>
       <c r="B209">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -6138,7 +6152,7 @@
         </is>
       </c>
       <c r="B210">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -6163,7 +6177,7 @@
         </is>
       </c>
       <c r="B211">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C211">
         <v>5</v>
@@ -6188,7 +6202,7 @@
         </is>
       </c>
       <c r="B212">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C212">
         <v>5</v>
@@ -6213,7 +6227,7 @@
         </is>
       </c>
       <c r="B213">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C213">
         <v>5</v>
@@ -6238,7 +6252,7 @@
         </is>
       </c>
       <c r="B214">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C214">
         <v>5</v>
@@ -6263,7 +6277,7 @@
         </is>
       </c>
       <c r="B215">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C215">
         <v>5</v>
@@ -6288,7 +6302,7 @@
         </is>
       </c>
       <c r="B216">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C216">
         <v>5</v>
@@ -6313,7 +6327,7 @@
         </is>
       </c>
       <c r="B217">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C217">
         <v>5</v>
@@ -6338,7 +6352,7 @@
         </is>
       </c>
       <c r="B218">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C218">
         <v>5</v>
@@ -6363,7 +6377,7 @@
         </is>
       </c>
       <c r="B219">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C219">
         <v>5</v>
@@ -6388,7 +6402,7 @@
         </is>
       </c>
       <c r="B220">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C220">
         <v>5</v>
@@ -6413,7 +6427,7 @@
         </is>
       </c>
       <c r="B221">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C221">
         <v>5</v>
@@ -6438,7 +6452,7 @@
         </is>
       </c>
       <c r="B222">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C222">
         <v>5</v>
@@ -6463,7 +6477,7 @@
         </is>
       </c>
       <c r="B223">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C223">
         <v>5</v>
@@ -6488,7 +6502,7 @@
         </is>
       </c>
       <c r="B224">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C224">
         <v>5</v>
@@ -6513,7 +6527,7 @@
         </is>
       </c>
       <c r="B225">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C225">
         <v>5</v>
@@ -6538,7 +6552,7 @@
         </is>
       </c>
       <c r="B226">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C226">
         <v>5</v>
@@ -6563,7 +6577,7 @@
         </is>
       </c>
       <c r="B227">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C227">
         <v>5</v>
@@ -6588,7 +6602,7 @@
         </is>
       </c>
       <c r="B228">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C228">
         <v>5</v>
@@ -6613,7 +6627,7 @@
         </is>
       </c>
       <c r="B229">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C229">
         <v>5</v>
@@ -6638,7 +6652,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C230">
         <v>5</v>
@@ -6663,7 +6677,7 @@
         </is>
       </c>
       <c r="B231">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C231">
         <v>5</v>
@@ -6688,7 +6702,7 @@
         </is>
       </c>
       <c r="B232">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C232">
         <v>5</v>
@@ -6713,7 +6727,7 @@
         </is>
       </c>
       <c r="B233">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C233">
         <v>5</v>
@@ -6738,7 +6752,7 @@
         </is>
       </c>
       <c r="B234">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C234">
         <v>5</v>
@@ -6763,7 +6777,7 @@
         </is>
       </c>
       <c r="B235">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C235">
         <v>5</v>
@@ -6788,7 +6802,7 @@
         </is>
       </c>
       <c r="B236">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C236">
         <v>5</v>
@@ -6813,7 +6827,7 @@
         </is>
       </c>
       <c r="B237">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C237">
         <v>5</v>
@@ -6838,7 +6852,7 @@
         </is>
       </c>
       <c r="B238">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C238">
         <v>5</v>
@@ -6863,7 +6877,7 @@
         </is>
       </c>
       <c r="B239">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C239">
         <v>5</v>
@@ -6888,7 +6902,7 @@
         </is>
       </c>
       <c r="B240">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C240">
         <v>5</v>
@@ -6913,7 +6927,7 @@
         </is>
       </c>
       <c r="B241">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C241">
         <v>5</v>
@@ -6938,7 +6952,7 @@
         </is>
       </c>
       <c r="B242">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C242">
         <v>5</v>
@@ -6963,7 +6977,7 @@
         </is>
       </c>
       <c r="B243">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C243">
         <v>5</v>
@@ -6988,7 +7002,7 @@
         </is>
       </c>
       <c r="B244">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C244">
         <v>5</v>
@@ -7013,7 +7027,7 @@
         </is>
       </c>
       <c r="B245">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C245">
         <v>5</v>
@@ -7038,7 +7052,7 @@
         </is>
       </c>
       <c r="B246">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C246">
         <v>5</v>
@@ -7063,7 +7077,7 @@
         </is>
       </c>
       <c r="B247">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C247">
         <v>5</v>
@@ -7088,7 +7102,7 @@
         </is>
       </c>
       <c r="B248">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C248">
         <v>5</v>
@@ -7113,7 +7127,7 @@
         </is>
       </c>
       <c r="B249">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C249">
         <v>5</v>
@@ -7138,7 +7152,7 @@
         </is>
       </c>
       <c r="B250">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C250">
         <v>5</v>
@@ -7163,7 +7177,7 @@
         </is>
       </c>
       <c r="B251">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C251">
         <v>5</v>
@@ -7188,7 +7202,7 @@
         </is>
       </c>
       <c r="B252">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C252">
         <v>5</v>
@@ -7213,7 +7227,7 @@
         </is>
       </c>
       <c r="B253">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C253">
         <v>5</v>
@@ -7238,7 +7252,7 @@
         </is>
       </c>
       <c r="B254">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C254">
         <v>5</v>
@@ -7263,7 +7277,7 @@
         </is>
       </c>
       <c r="B255">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C255">
         <v>5</v>
@@ -7288,7 +7302,7 @@
         </is>
       </c>
       <c r="B256">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C256">
         <v>5</v>
@@ -7313,7 +7327,7 @@
         </is>
       </c>
       <c r="B257">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C257">
         <v>5</v>
@@ -7338,7 +7352,7 @@
         </is>
       </c>
       <c r="B258">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C258">
         <v>5</v>
@@ -7363,7 +7377,7 @@
         </is>
       </c>
       <c r="B259">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C259">
         <v>5</v>
@@ -7388,7 +7402,7 @@
         </is>
       </c>
       <c r="B260">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C260">
         <v>5</v>
@@ -7413,7 +7427,7 @@
         </is>
       </c>
       <c r="B261">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C261">
         <v>5</v>
@@ -7438,7 +7452,7 @@
         </is>
       </c>
       <c r="B262">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C262">
         <v>5</v>
@@ -7463,7 +7477,7 @@
         </is>
       </c>
       <c r="B263">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C263">
         <v>5</v>
@@ -7488,7 +7502,7 @@
         </is>
       </c>
       <c r="B264">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C264">
         <v>5</v>
@@ -7513,7 +7527,7 @@
         </is>
       </c>
       <c r="B265">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C265">
         <v>5</v>
@@ -7538,7 +7552,7 @@
         </is>
       </c>
       <c r="B266">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C266">
         <v>5</v>
@@ -7563,7 +7577,7 @@
         </is>
       </c>
       <c r="B267">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C267">
         <v>5</v>
@@ -7588,7 +7602,7 @@
         </is>
       </c>
       <c r="B268">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C268">
         <v>5</v>
@@ -7613,7 +7627,7 @@
         </is>
       </c>
       <c r="B269">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C269">
         <v>5</v>
@@ -7638,7 +7652,7 @@
         </is>
       </c>
       <c r="B270">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C270">
         <v>5</v>
@@ -7663,7 +7677,7 @@
         </is>
       </c>
       <c r="B271">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C271">
         <v>5</v>
@@ -7688,7 +7702,7 @@
         </is>
       </c>
       <c r="B272">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C272">
         <v>5</v>
@@ -7713,7 +7727,7 @@
         </is>
       </c>
       <c r="B273">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C273">
         <v>5</v>
@@ -7738,7 +7752,7 @@
         </is>
       </c>
       <c r="B274">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C274">
         <v>5</v>
@@ -7763,7 +7777,7 @@
         </is>
       </c>
       <c r="B275">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C275">
         <v>5</v>
@@ -7788,7 +7802,7 @@
         </is>
       </c>
       <c r="B276">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C276">
         <v>5</v>
@@ -7813,7 +7827,7 @@
         </is>
       </c>
       <c r="B277">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C277">
         <v>5</v>
@@ -7838,7 +7852,7 @@
         </is>
       </c>
       <c r="B278">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C278">
         <v>5</v>
@@ -7863,7 +7877,7 @@
         </is>
       </c>
       <c r="B279">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C279">
         <v>5</v>
@@ -7888,7 +7902,7 @@
         </is>
       </c>
       <c r="B280">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -7913,7 +7927,7 @@
         </is>
       </c>
       <c r="B281">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -7938,7 +7952,7 @@
         </is>
       </c>
       <c r="B282">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -7963,7 +7977,7 @@
         </is>
       </c>
       <c r="B283">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -7988,7 +8002,7 @@
         </is>
       </c>
       <c r="B284">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -8013,7 +8027,7 @@
         </is>
       </c>
       <c r="B285">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8038,7 +8052,7 @@
         </is>
       </c>
       <c r="B286">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -8063,7 +8077,7 @@
         </is>
       </c>
       <c r="B287">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C287">
         <v>5</v>
@@ -8088,7 +8102,7 @@
         </is>
       </c>
       <c r="B288">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C288">
         <v>5</v>
@@ -8113,7 +8127,7 @@
         </is>
       </c>
       <c r="B289">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C289">
         <v>5</v>
@@ -8138,7 +8152,7 @@
         </is>
       </c>
       <c r="B290">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C290">
         <v>5</v>
@@ -8163,7 +8177,7 @@
         </is>
       </c>
       <c r="B291">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C291">
         <v>5</v>
@@ -8188,7 +8202,7 @@
         </is>
       </c>
       <c r="B292">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C292">
         <v>5</v>
@@ -8213,7 +8227,7 @@
         </is>
       </c>
       <c r="B293">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C293">
         <v>5</v>
@@ -8238,7 +8252,7 @@
         </is>
       </c>
       <c r="B294">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C294">
         <v>5</v>
@@ -8263,7 +8277,7 @@
         </is>
       </c>
       <c r="B295">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C295">
         <v>5</v>
@@ -8288,7 +8302,7 @@
         </is>
       </c>
       <c r="B296">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C296">
         <v>5</v>
@@ -8313,7 +8327,7 @@
         </is>
       </c>
       <c r="B297">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C297">
         <v>5</v>
@@ -8338,7 +8352,7 @@
         </is>
       </c>
       <c r="B298">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C298">
         <v>5</v>
@@ -8363,7 +8377,7 @@
         </is>
       </c>
       <c r="B299">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C299">
         <v>5</v>
@@ -8388,7 +8402,7 @@
         </is>
       </c>
       <c r="B300">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C300">
         <v>5</v>
@@ -8413,7 +8427,7 @@
         </is>
       </c>
       <c r="B301">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C301">
         <v>5</v>
@@ -8438,7 +8452,7 @@
         </is>
       </c>
       <c r="B302">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C302">
         <v>5</v>
@@ -8463,7 +8477,7 @@
         </is>
       </c>
       <c r="B303">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C303">
         <v>5</v>
@@ -8488,7 +8502,7 @@
         </is>
       </c>
       <c r="B304">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C304">
         <v>5</v>
@@ -8513,7 +8527,7 @@
         </is>
       </c>
       <c r="B305">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C305">
         <v>5</v>
@@ -8538,7 +8552,7 @@
         </is>
       </c>
       <c r="B306">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C306">
         <v>5</v>
@@ -8563,7 +8577,7 @@
         </is>
       </c>
       <c r="B307">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C307">
         <v>5</v>
@@ -8588,7 +8602,7 @@
         </is>
       </c>
       <c r="B308">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C308">
         <v>5</v>
@@ -8613,7 +8627,7 @@
         </is>
       </c>
       <c r="B309">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C309">
         <v>5</v>
@@ -8638,7 +8652,7 @@
         </is>
       </c>
       <c r="B310">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C310">
         <v>5</v>
@@ -8663,7 +8677,7 @@
         </is>
       </c>
       <c r="B311">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C311">
         <v>5</v>
@@ -8688,7 +8702,7 @@
         </is>
       </c>
       <c r="B312">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C312">
         <v>5</v>
@@ -8713,7 +8727,7 @@
         </is>
       </c>
       <c r="B313">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C313">
         <v>5</v>
@@ -8738,7 +8752,7 @@
         </is>
       </c>
       <c r="B314">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C314">
         <v>5</v>
@@ -8763,7 +8777,7 @@
         </is>
       </c>
       <c r="B315">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C315">
         <v>5</v>
@@ -8788,7 +8802,7 @@
         </is>
       </c>
       <c r="B316">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C316">
         <v>5</v>
@@ -8813,7 +8827,7 @@
         </is>
       </c>
       <c r="B317">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C317">
         <v>5</v>
@@ -8838,7 +8852,7 @@
         </is>
       </c>
       <c r="B318">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C318">
         <v>5</v>
@@ -8863,7 +8877,7 @@
         </is>
       </c>
       <c r="B319">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C319">
         <v>5</v>
@@ -8888,7 +8902,7 @@
         </is>
       </c>
       <c r="B320">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C320">
         <v>5</v>
@@ -8913,7 +8927,7 @@
         </is>
       </c>
       <c r="B321">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C321">
         <v>5</v>
@@ -8938,7 +8952,7 @@
         </is>
       </c>
       <c r="B322">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C322">
         <v>5</v>
@@ -8963,7 +8977,7 @@
         </is>
       </c>
       <c r="B323">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C323">
         <v>5</v>
@@ -8988,7 +9002,7 @@
         </is>
       </c>
       <c r="B324">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C324">
         <v>5</v>
@@ -9013,7 +9027,7 @@
         </is>
       </c>
       <c r="B325">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C325">
         <v>5</v>
@@ -9038,7 +9052,7 @@
         </is>
       </c>
       <c r="B326">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C326">
         <v>5</v>
@@ -9063,7 +9077,7 @@
         </is>
       </c>
       <c r="B327">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C327">
         <v>5</v>
@@ -9088,7 +9102,7 @@
         </is>
       </c>
       <c r="B328">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C328">
         <v>5</v>
@@ -9113,7 +9127,7 @@
         </is>
       </c>
       <c r="B329">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C329">
         <v>5</v>
@@ -9138,7 +9152,7 @@
         </is>
       </c>
       <c r="B330">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C330">
         <v>5</v>
@@ -9163,7 +9177,7 @@
         </is>
       </c>
       <c r="B331">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C331">
         <v>5</v>
@@ -9188,7 +9202,7 @@
         </is>
       </c>
       <c r="B332">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C332">
         <v>5</v>
@@ -9213,7 +9227,7 @@
         </is>
       </c>
       <c r="B333">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C333">
         <v>5</v>
@@ -9238,7 +9252,7 @@
         </is>
       </c>
       <c r="B334">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C334">
         <v>5</v>
@@ -9263,7 +9277,7 @@
         </is>
       </c>
       <c r="B335">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C335">
         <v>5</v>
@@ -9288,7 +9302,7 @@
         </is>
       </c>
       <c r="B336">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C336">
         <v>5</v>
@@ -9313,7 +9327,7 @@
         </is>
       </c>
       <c r="B337">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C337">
         <v>5</v>
@@ -9338,7 +9352,7 @@
         </is>
       </c>
       <c r="B338">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C338">
         <v>5</v>
@@ -9363,7 +9377,7 @@
         </is>
       </c>
       <c r="B339">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C339">
         <v>5</v>
@@ -9388,7 +9402,7 @@
         </is>
       </c>
       <c r="B340">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C340">
         <v>5</v>
@@ -9413,7 +9427,7 @@
         </is>
       </c>
       <c r="B341">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C341">
         <v>5</v>
@@ -9438,7 +9452,7 @@
         </is>
       </c>
       <c r="B342">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C342">
         <v>5</v>
@@ -9463,7 +9477,7 @@
         </is>
       </c>
       <c r="B343">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C343">
         <v>5</v>
@@ -9488,7 +9502,7 @@
         </is>
       </c>
       <c r="B344">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C344">
         <v>5</v>
@@ -9513,7 +9527,7 @@
         </is>
       </c>
       <c r="B345">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C345">
         <v>5</v>
@@ -9538,7 +9552,7 @@
         </is>
       </c>
       <c r="B346">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C346">
         <v>5</v>
@@ -9563,7 +9577,7 @@
         </is>
       </c>
       <c r="B347">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C347">
         <v>5</v>
@@ -9588,7 +9602,7 @@
         </is>
       </c>
       <c r="B348">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C348">
         <v>5</v>
@@ -9613,7 +9627,7 @@
         </is>
       </c>
       <c r="B349">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C349">
         <v>5</v>
@@ -9638,7 +9652,7 @@
         </is>
       </c>
       <c r="B350">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C350">
         <v>5</v>
@@ -9663,7 +9677,7 @@
         </is>
       </c>
       <c r="B351">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C351">
         <v>5</v>
@@ -9688,7 +9702,7 @@
         </is>
       </c>
       <c r="B352">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C352">
         <v>5</v>
@@ -9713,7 +9727,7 @@
         </is>
       </c>
       <c r="B353">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C353">
         <v>5</v>
@@ -9738,7 +9752,7 @@
         </is>
       </c>
       <c r="B354">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C354">
         <v>5</v>
@@ -9763,7 +9777,7 @@
         </is>
       </c>
       <c r="B355">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C355">
         <v>5</v>
@@ -9788,7 +9802,7 @@
         </is>
       </c>
       <c r="B356">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C356">
         <v>5</v>
@@ -9813,7 +9827,7 @@
         </is>
       </c>
       <c r="B357">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C357">
         <v>5</v>
@@ -9838,7 +9852,7 @@
         </is>
       </c>
       <c r="B358">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C358">
         <v>5</v>
@@ -9863,7 +9877,7 @@
         </is>
       </c>
       <c r="B359">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C359">
         <v>5</v>
@@ -9888,7 +9902,7 @@
         </is>
       </c>
       <c r="B360">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C360">
         <v>5</v>
@@ -9913,7 +9927,7 @@
         </is>
       </c>
       <c r="B361">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C361">
         <v>5</v>
@@ -9938,7 +9952,7 @@
         </is>
       </c>
       <c r="B362">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C362">
         <v>5</v>
@@ -9963,7 +9977,7 @@
         </is>
       </c>
       <c r="B363">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C363">
         <v>5</v>
@@ -9988,7 +10002,7 @@
         </is>
       </c>
       <c r="B364">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C364">
         <v>5</v>
@@ -10013,7 +10027,7 @@
         </is>
       </c>
       <c r="B365">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C365">
         <v>5</v>
@@ -10038,7 +10052,7 @@
         </is>
       </c>
       <c r="B366">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C366">
         <v>5</v>
@@ -10063,7 +10077,7 @@
         </is>
       </c>
       <c r="B367">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C367">
         <v>5</v>
@@ -10088,7 +10102,7 @@
         </is>
       </c>
       <c r="B368">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C368">
         <v>5</v>
@@ -10113,7 +10127,7 @@
         </is>
       </c>
       <c r="B369">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C369">
         <v>5</v>
@@ -10138,7 +10152,7 @@
         </is>
       </c>
       <c r="B370">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C370">
         <v>5</v>
@@ -10163,7 +10177,7 @@
         </is>
       </c>
       <c r="B371">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C371">
         <v>5</v>
@@ -10188,7 +10202,7 @@
         </is>
       </c>
       <c r="B372">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C372">
         <v>5</v>
@@ -10213,7 +10227,7 @@
         </is>
       </c>
       <c r="B373">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C373">
         <v>5</v>
@@ -10238,7 +10252,7 @@
         </is>
       </c>
       <c r="B374">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C374">
         <v>5</v>
@@ -10263,7 +10277,7 @@
         </is>
       </c>
       <c r="B375">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C375">
         <v>5</v>
@@ -10288,7 +10302,7 @@
         </is>
       </c>
       <c r="B376">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C376">
         <v>5</v>
@@ -10313,7 +10327,7 @@
         </is>
       </c>
       <c r="B377">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C377">
         <v>5</v>
@@ -10338,7 +10352,7 @@
         </is>
       </c>
       <c r="B378">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C378">
         <v>5</v>
@@ -10363,7 +10377,7 @@
         </is>
       </c>
       <c r="B379">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C379">
         <v>5</v>
@@ -10388,7 +10402,7 @@
         </is>
       </c>
       <c r="B380">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C380">
         <v>5</v>
@@ -10413,7 +10427,7 @@
         </is>
       </c>
       <c r="B381">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C381">
         <v>5</v>
@@ -10438,7 +10452,7 @@
         </is>
       </c>
       <c r="B382">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C382">
         <v>5</v>
@@ -10463,7 +10477,7 @@
         </is>
       </c>
       <c r="B383">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C383">
         <v>5</v>
@@ -10488,7 +10502,7 @@
         </is>
       </c>
       <c r="B384">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C384">
         <v>5</v>
@@ -10513,7 +10527,7 @@
         </is>
       </c>
       <c r="B385">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C385">
         <v>5</v>
@@ -10538,7 +10552,7 @@
         </is>
       </c>
       <c r="B386">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C386">
         <v>5</v>
@@ -10563,7 +10577,7 @@
         </is>
       </c>
       <c r="B387">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C387">
         <v>5</v>
@@ -10588,7 +10602,7 @@
         </is>
       </c>
       <c r="B388">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C388">
         <v>5</v>
@@ -10613,7 +10627,7 @@
         </is>
       </c>
       <c r="B389">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C389">
         <v>5</v>
@@ -10638,7 +10652,7 @@
         </is>
       </c>
       <c r="B390">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C390">
         <v>5</v>
@@ -10663,7 +10677,7 @@
         </is>
       </c>
       <c r="B391">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C391">
         <v>5</v>
@@ -10688,7 +10702,7 @@
         </is>
       </c>
       <c r="B392">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C392">
         <v>5</v>
@@ -10713,7 +10727,7 @@
         </is>
       </c>
       <c r="B393">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C393">
         <v>5</v>
@@ -10738,7 +10752,7 @@
         </is>
       </c>
       <c r="B394">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C394">
         <v>5</v>
@@ -10763,7 +10777,7 @@
         </is>
       </c>
       <c r="B395">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C395">
         <v>5</v>
@@ -10788,7 +10802,7 @@
         </is>
       </c>
       <c r="B396">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C396">
         <v>5</v>
@@ -10813,7 +10827,7 @@
         </is>
       </c>
       <c r="B397">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C397">
         <v>5</v>
@@ -10838,7 +10852,7 @@
         </is>
       </c>
       <c r="B398">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C398">
         <v>5</v>
@@ -10863,7 +10877,7 @@
         </is>
       </c>
       <c r="B399">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C399">
         <v>5</v>
@@ -10888,7 +10902,7 @@
         </is>
       </c>
       <c r="B400">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C400">
         <v>5</v>
@@ -10913,7 +10927,7 @@
         </is>
       </c>
       <c r="B401">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C401">
         <v>5</v>
@@ -10938,7 +10952,7 @@
         </is>
       </c>
       <c r="B402">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C402">
         <v>5</v>
@@ -10963,7 +10977,7 @@
         </is>
       </c>
       <c r="B403">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C403">
         <v>5</v>
@@ -10988,7 +11002,7 @@
         </is>
       </c>
       <c r="B404">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C404">
         <v>5</v>
@@ -11013,7 +11027,7 @@
         </is>
       </c>
       <c r="B405">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C405">
         <v>5</v>
@@ -11038,7 +11052,7 @@
         </is>
       </c>
       <c r="B406">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C406">
         <v>5</v>
@@ -11063,7 +11077,7 @@
         </is>
       </c>
       <c r="B407">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C407">
         <v>5</v>
@@ -11088,7 +11102,7 @@
         </is>
       </c>
       <c r="B408">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C408">
         <v>5</v>
@@ -11113,7 +11127,7 @@
         </is>
       </c>
       <c r="B409">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C409">
         <v>5</v>
@@ -11138,7 +11152,7 @@
         </is>
       </c>
       <c r="B410">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C410">
         <v>5</v>
@@ -11163,7 +11177,7 @@
         </is>
       </c>
       <c r="B411">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C411">
         <v>5</v>
@@ -11188,7 +11202,7 @@
         </is>
       </c>
       <c r="B412">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C412">
         <v>5</v>
@@ -11213,7 +11227,7 @@
         </is>
       </c>
       <c r="B413">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C413">
         <v>5</v>
@@ -11238,7 +11252,7 @@
         </is>
       </c>
       <c r="B414">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C414">
         <v>5</v>
@@ -11263,7 +11277,7 @@
         </is>
       </c>
       <c r="B415">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C415">
         <v>5</v>
@@ -11288,7 +11302,7 @@
         </is>
       </c>
       <c r="B416">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C416">
         <v>5</v>
@@ -11313,7 +11327,7 @@
         </is>
       </c>
       <c r="B417">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C417">
         <v>5</v>
@@ -11338,7 +11352,7 @@
         </is>
       </c>
       <c r="B418">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C418">
         <v>5</v>
@@ -11363,7 +11377,7 @@
         </is>
       </c>
       <c r="B419">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C419">
         <v>5</v>
@@ -11388,7 +11402,7 @@
         </is>
       </c>
       <c r="B420">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C420">
         <v>5</v>
@@ -11413,7 +11427,7 @@
         </is>
       </c>
       <c r="B421">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C421">
         <v>5</v>
@@ -11438,7 +11452,7 @@
         </is>
       </c>
       <c r="B422">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C422">
         <v>5</v>
@@ -11463,7 +11477,7 @@
         </is>
       </c>
       <c r="B423">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C423">
         <v>5</v>
@@ -11488,7 +11502,7 @@
         </is>
       </c>
       <c r="B424">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C424">
         <v>5</v>
@@ -11513,7 +11527,7 @@
         </is>
       </c>
       <c r="B425">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C425">
         <v>5</v>
@@ -11538,7 +11552,7 @@
         </is>
       </c>
       <c r="B426">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C426">
         <v>5</v>
@@ -11563,7 +11577,7 @@
         </is>
       </c>
       <c r="B427">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C427">
         <v>5</v>
@@ -11588,7 +11602,7 @@
         </is>
       </c>
       <c r="B428">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C428">
         <v>5</v>
@@ -11613,7 +11627,7 @@
         </is>
       </c>
       <c r="B429">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C429">
         <v>5</v>
@@ -11638,7 +11652,7 @@
         </is>
       </c>
       <c r="B430">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C430">
         <v>5</v>
@@ -11663,7 +11677,7 @@
         </is>
       </c>
       <c r="B431">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C431">
         <v>5</v>
@@ -11688,7 +11702,7 @@
         </is>
       </c>
       <c r="B432">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C432">
         <v>5</v>
@@ -11713,7 +11727,7 @@
         </is>
       </c>
       <c r="B433">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C433">
         <v>5</v>
@@ -11738,7 +11752,7 @@
         </is>
       </c>
       <c r="B434">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C434">
         <v>5</v>
@@ -11763,7 +11777,7 @@
         </is>
       </c>
       <c r="B435">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C435">
         <v>5</v>
@@ -11788,7 +11802,7 @@
         </is>
       </c>
       <c r="B436">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C436">
         <v>5</v>
@@ -11813,7 +11827,7 @@
         </is>
       </c>
       <c r="B437">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C437">
         <v>5</v>
@@ -11838,7 +11852,7 @@
         </is>
       </c>
       <c r="B438">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C438">
         <v>5</v>
@@ -11863,7 +11877,7 @@
         </is>
       </c>
       <c r="B439">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C439">
         <v>5</v>
@@ -11888,7 +11902,7 @@
         </is>
       </c>
       <c r="B440">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C440">
         <v>5</v>
@@ -11913,7 +11927,7 @@
         </is>
       </c>
       <c r="B441">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C441">
         <v>5</v>
@@ -11938,7 +11952,7 @@
         </is>
       </c>
       <c r="B442">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C442">
         <v>5</v>
@@ -11963,7 +11977,7 @@
         </is>
       </c>
       <c r="B443">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C443">
         <v>5</v>
@@ -11988,7 +12002,7 @@
         </is>
       </c>
       <c r="B444">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C444">
         <v>5</v>
@@ -12013,7 +12027,7 @@
         </is>
       </c>
       <c r="B445">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C445">
         <v>5</v>
@@ -12038,7 +12052,7 @@
         </is>
       </c>
       <c r="B446">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C446">
         <v>5</v>
@@ -12063,7 +12077,7 @@
         </is>
       </c>
       <c r="B447">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C447">
         <v>5</v>
@@ -12088,7 +12102,7 @@
         </is>
       </c>
       <c r="B448">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C448">
         <v>5</v>
@@ -12113,7 +12127,7 @@
         </is>
       </c>
       <c r="B449">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C449">
         <v>5</v>
@@ -12138,7 +12152,7 @@
         </is>
       </c>
       <c r="B450">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C450">
         <v>5</v>
@@ -12163,7 +12177,7 @@
         </is>
       </c>
       <c r="B451">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C451">
         <v>5</v>
@@ -12188,7 +12202,7 @@
         </is>
       </c>
       <c r="B452">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C452">
         <v>5</v>
@@ -12213,7 +12227,7 @@
         </is>
       </c>
       <c r="B453">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C453">
         <v>5</v>
@@ -12238,7 +12252,7 @@
         </is>
       </c>
       <c r="B454">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C454">
         <v>5</v>
@@ -12263,7 +12277,7 @@
         </is>
       </c>
       <c r="B455">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C455">
         <v>5</v>
@@ -12288,7 +12302,7 @@
         </is>
       </c>
       <c r="B456">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C456">
         <v>5</v>
@@ -12313,7 +12327,7 @@
         </is>
       </c>
       <c r="B457">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C457">
         <v>5</v>
@@ -12338,7 +12352,7 @@
         </is>
       </c>
       <c r="B458">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C458">
         <v>5</v>
@@ -12363,7 +12377,7 @@
         </is>
       </c>
       <c r="B459">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C459">
         <v>5</v>
@@ -12388,7 +12402,7 @@
         </is>
       </c>
       <c r="B460">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C460">
         <v>5</v>
@@ -12413,7 +12427,7 @@
         </is>
       </c>
       <c r="B461">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C461">
         <v>5</v>
@@ -12438,7 +12452,7 @@
         </is>
       </c>
       <c r="B462">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C462">
         <v>5</v>
@@ -12463,7 +12477,7 @@
         </is>
       </c>
       <c r="B463">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C463">
         <v>5</v>
@@ -12488,7 +12502,7 @@
         </is>
       </c>
       <c r="B464">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C464">
         <v>5</v>
@@ -12513,7 +12527,7 @@
         </is>
       </c>
       <c r="B465">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C465">
         <v>5</v>
@@ -12538,7 +12552,7 @@
         </is>
       </c>
       <c r="B466">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C466">
         <v>5</v>
@@ -12563,7 +12577,7 @@
         </is>
       </c>
       <c r="B467">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C467">
         <v>5</v>
@@ -12588,7 +12602,7 @@
         </is>
       </c>
       <c r="B468">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C468">
         <v>5</v>
@@ -12613,7 +12627,7 @@
         </is>
       </c>
       <c r="B469">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C469">
         <v>5</v>
@@ -12638,7 +12652,7 @@
         </is>
       </c>
       <c r="B470">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C470">
         <v>5</v>
@@ -12663,7 +12677,7 @@
         </is>
       </c>
       <c r="B471">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C471">
         <v>5</v>
@@ -12688,7 +12702,7 @@
         </is>
       </c>
       <c r="B472">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C472">
         <v>5</v>
@@ -12713,7 +12727,7 @@
         </is>
       </c>
       <c r="B473">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C473">
         <v>5</v>
@@ -12738,7 +12752,7 @@
         </is>
       </c>
       <c r="B474">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C474">
         <v>5</v>
@@ -12763,7 +12777,7 @@
         </is>
       </c>
       <c r="B475">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C475">
         <v>5</v>
@@ -12788,7 +12802,7 @@
         </is>
       </c>
       <c r="B476">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C476">
         <v>5</v>
@@ -12813,7 +12827,7 @@
         </is>
       </c>
       <c r="B477">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C477">
         <v>5</v>
@@ -12838,7 +12852,7 @@
         </is>
       </c>
       <c r="B478">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C478">
         <v>5</v>
@@ -12863,7 +12877,7 @@
         </is>
       </c>
       <c r="B479">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C479">
         <v>5</v>
@@ -12888,7 +12902,7 @@
         </is>
       </c>
       <c r="B480">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C480">
         <v>5</v>
@@ -12913,7 +12927,7 @@
         </is>
       </c>
       <c r="B481">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C481">
         <v>5</v>
@@ -12938,7 +12952,7 @@
         </is>
       </c>
       <c r="B482">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C482">
         <v>5</v>
@@ -12963,7 +12977,7 @@
         </is>
       </c>
       <c r="B483">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C483">
         <v>5</v>
@@ -12988,7 +13002,7 @@
         </is>
       </c>
       <c r="B484">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C484">
         <v>5</v>
@@ -13013,7 +13027,7 @@
         </is>
       </c>
       <c r="B485">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C485">
         <v>5</v>
@@ -13038,7 +13052,7 @@
         </is>
       </c>
       <c r="B486">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C486">
         <v>5</v>
@@ -13063,7 +13077,7 @@
         </is>
       </c>
       <c r="B487">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C487">
         <v>5</v>
@@ -13088,7 +13102,7 @@
         </is>
       </c>
       <c r="B488">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C488">
         <v>5</v>
@@ -13113,7 +13127,7 @@
         </is>
       </c>
       <c r="B489">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C489">
         <v>5</v>
@@ -13138,7 +13152,7 @@
         </is>
       </c>
       <c r="B490">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C490">
         <v>5</v>
@@ -13163,7 +13177,7 @@
         </is>
       </c>
       <c r="B491">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C491">
         <v>5</v>
@@ -13188,7 +13202,7 @@
         </is>
       </c>
       <c r="B492">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C492">
         <v>5</v>
@@ -13213,7 +13227,7 @@
         </is>
       </c>
       <c r="B493">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C493">
         <v>5</v>
@@ -13238,7 +13252,7 @@
         </is>
       </c>
       <c r="B494">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C494">
         <v>5</v>
@@ -13263,7 +13277,7 @@
         </is>
       </c>
       <c r="B495">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C495">
         <v>5</v>
@@ -13288,7 +13302,7 @@
         </is>
       </c>
       <c r="B496">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C496">
         <v>5</v>
@@ -13313,7 +13327,7 @@
         </is>
       </c>
       <c r="B497">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C497">
         <v>5</v>
@@ -13338,7 +13352,7 @@
         </is>
       </c>
       <c r="B498">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C498">
         <v>5</v>
@@ -13363,7 +13377,7 @@
         </is>
       </c>
       <c r="B499">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C499">
         <v>5</v>
@@ -13388,7 +13402,7 @@
         </is>
       </c>
       <c r="B500">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C500">
         <v>5</v>
@@ -13413,7 +13427,7 @@
         </is>
       </c>
       <c r="B501">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C501">
         <v>5</v>
@@ -13438,7 +13452,7 @@
         </is>
       </c>
       <c r="B502">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C502">
         <v>5</v>
@@ -13463,7 +13477,7 @@
         </is>
       </c>
       <c r="B503">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C503">
         <v>5</v>
@@ -13488,7 +13502,7 @@
         </is>
       </c>
       <c r="B504">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C504">
         <v>5</v>
@@ -13513,7 +13527,7 @@
         </is>
       </c>
       <c r="B505">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C505">
         <v>5</v>
@@ -13538,7 +13552,7 @@
         </is>
       </c>
       <c r="B506">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C506">
         <v>5</v>
@@ -13563,7 +13577,7 @@
         </is>
       </c>
       <c r="B507">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C507">
         <v>5</v>
@@ -13588,7 +13602,7 @@
         </is>
       </c>
       <c r="B508">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C508">
         <v>5</v>
@@ -13613,7 +13627,7 @@
         </is>
       </c>
       <c r="B509">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C509">
         <v>5</v>
@@ -13638,7 +13652,7 @@
         </is>
       </c>
       <c r="B510">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C510">
         <v>5</v>
@@ -13663,7 +13677,7 @@
         </is>
       </c>
       <c r="B511">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C511">
         <v>5</v>
@@ -13688,7 +13702,7 @@
         </is>
       </c>
       <c r="B512">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C512">
         <v>5</v>
@@ -13713,7 +13727,7 @@
         </is>
       </c>
       <c r="B513">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C513">
         <v>5</v>
@@ -13738,7 +13752,7 @@
         </is>
       </c>
       <c r="B514">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C514">
         <v>5</v>
@@ -13763,7 +13777,7 @@
         </is>
       </c>
       <c r="B515">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C515">
         <v>5</v>
@@ -13788,7 +13802,7 @@
         </is>
       </c>
       <c r="B516">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C516">
         <v>5</v>
@@ -13813,7 +13827,7 @@
         </is>
       </c>
       <c r="B517">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C517">
         <v>5</v>
@@ -13838,7 +13852,7 @@
         </is>
       </c>
       <c r="B518">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C518">
         <v>5</v>
@@ -13863,7 +13877,7 @@
         </is>
       </c>
       <c r="B519">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C519">
         <v>5</v>
@@ -13888,7 +13902,7 @@
         </is>
       </c>
       <c r="B520">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C520">
         <v>5</v>
@@ -13913,7 +13927,7 @@
         </is>
       </c>
       <c r="B521">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C521">
         <v>5</v>
@@ -13938,7 +13952,7 @@
         </is>
       </c>
       <c r="B522">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C522">
         <v>5</v>
@@ -13963,7 +13977,7 @@
         </is>
       </c>
       <c r="B523">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C523">
         <v>5</v>
@@ -13988,7 +14002,7 @@
         </is>
       </c>
       <c r="B524">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C524">
         <v>5</v>
@@ -14013,7 +14027,7 @@
         </is>
       </c>
       <c r="B525">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C525">
         <v>5</v>
@@ -14038,7 +14052,7 @@
         </is>
       </c>
       <c r="B526">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C526">
         <v>5</v>
@@ -14063,7 +14077,7 @@
         </is>
       </c>
       <c r="B527">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C527">
         <v>5</v>
@@ -14088,7 +14102,7 @@
         </is>
       </c>
       <c r="B528">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C528">
         <v>5</v>
@@ -14113,7 +14127,7 @@
         </is>
       </c>
       <c r="B529">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C529">
         <v>5</v>
@@ -14138,7 +14152,7 @@
         </is>
       </c>
       <c r="B530">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C530">
         <v>5</v>
@@ -14163,7 +14177,7 @@
         </is>
       </c>
       <c r="B531">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C531">
         <v>5</v>
@@ -14188,7 +14202,7 @@
         </is>
       </c>
       <c r="B532">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C532">
         <v>5</v>
@@ -14213,7 +14227,7 @@
         </is>
       </c>
       <c r="B533">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C533">
         <v>5</v>
@@ -14238,7 +14252,7 @@
         </is>
       </c>
       <c r="B534">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C534">
         <v>5</v>
@@ -14263,7 +14277,7 @@
         </is>
       </c>
       <c r="B535">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C535">
         <v>5</v>
@@ -14288,7 +14302,7 @@
         </is>
       </c>
       <c r="B536">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C536">
         <v>5</v>
@@ -14313,7 +14327,7 @@
         </is>
       </c>
       <c r="B537">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C537">
         <v>5</v>
@@ -14338,7 +14352,7 @@
         </is>
       </c>
       <c r="B538">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C538">
         <v>5</v>
@@ -14363,7 +14377,7 @@
         </is>
       </c>
       <c r="B539">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C539">
         <v>5</v>
@@ -14388,7 +14402,7 @@
         </is>
       </c>
       <c r="B540">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C540">
         <v>5</v>
@@ -14413,7 +14427,7 @@
         </is>
       </c>
       <c r="B541">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C541">
         <v>5</v>
@@ -14438,7 +14452,7 @@
         </is>
       </c>
       <c r="B542">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C542">
         <v>5</v>
@@ -14463,7 +14477,7 @@
         </is>
       </c>
       <c r="B543">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C543">
         <v>5</v>
@@ -14488,7 +14502,7 @@
         </is>
       </c>
       <c r="B544">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C544">
         <v>5</v>
@@ -14513,7 +14527,7 @@
         </is>
       </c>
       <c r="B545">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C545">
         <v>5</v>
@@ -14538,7 +14552,7 @@
         </is>
       </c>
       <c r="B546">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C546">
         <v>5</v>
@@ -14563,7 +14577,7 @@
         </is>
       </c>
       <c r="B547">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C547">
         <v>5</v>
@@ -14588,7 +14602,7 @@
         </is>
       </c>
       <c r="B548">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C548">
         <v>5</v>
@@ -14613,7 +14627,7 @@
         </is>
       </c>
       <c r="B549">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C549">
         <v>5</v>
@@ -14638,7 +14652,7 @@
         </is>
       </c>
       <c r="B550">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C550">
         <v>5</v>
@@ -14663,7 +14677,7 @@
         </is>
       </c>
       <c r="B551">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C551">
         <v>5</v>
@@ -14688,7 +14702,7 @@
         </is>
       </c>
       <c r="B552">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C552">
         <v>5</v>
@@ -14713,7 +14727,7 @@
         </is>
       </c>
       <c r="B553">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C553">
         <v>5</v>
@@ -14738,7 +14752,7 @@
         </is>
       </c>
       <c r="B554">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C554">
         <v>5</v>
@@ -14763,7 +14777,7 @@
         </is>
       </c>
       <c r="B555">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C555">
         <v>5</v>
@@ -14788,7 +14802,7 @@
         </is>
       </c>
       <c r="B556">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C556">
         <v>5</v>
@@ -14813,7 +14827,7 @@
         </is>
       </c>
       <c r="B557">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C557">
         <v>5</v>
@@ -14838,7 +14852,7 @@
         </is>
       </c>
       <c r="B558">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C558">
         <v>5</v>
@@ -14863,7 +14877,7 @@
         </is>
       </c>
       <c r="B559">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C559">
         <v>5</v>
@@ -14888,7 +14902,7 @@
         </is>
       </c>
       <c r="B560">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C560">
         <v>5</v>
@@ -14913,7 +14927,7 @@
         </is>
       </c>
       <c r="B561">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C561">
         <v>5</v>
@@ -14938,7 +14952,7 @@
         </is>
       </c>
       <c r="B562">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C562">
         <v>5</v>
@@ -14963,7 +14977,7 @@
         </is>
       </c>
       <c r="B563">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C563">
         <v>5</v>
@@ -14988,7 +15002,7 @@
         </is>
       </c>
       <c r="B564">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C564">
         <v>5</v>
@@ -15013,7 +15027,7 @@
         </is>
       </c>
       <c r="B565">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C565">
         <v>5</v>
@@ -15038,7 +15052,7 @@
         </is>
       </c>
       <c r="B566">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C566">
         <v>5</v>
@@ -15063,7 +15077,7 @@
         </is>
       </c>
       <c r="B567">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C567">
         <v>5</v>
@@ -15088,7 +15102,7 @@
         </is>
       </c>
       <c r="B568">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C568">
         <v>5</v>
@@ -15113,7 +15127,7 @@
         </is>
       </c>
       <c r="B569">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C569">
         <v>5</v>
@@ -15138,7 +15152,7 @@
         </is>
       </c>
       <c r="B570">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C570">
         <v>5</v>
@@ -15163,7 +15177,7 @@
         </is>
       </c>
       <c r="B571">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C571">
         <v>5</v>
@@ -15188,7 +15202,7 @@
         </is>
       </c>
       <c r="B572">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C572">
         <v>5</v>
@@ -15213,7 +15227,7 @@
         </is>
       </c>
       <c r="B573">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C573">
         <v>5</v>
@@ -15238,7 +15252,7 @@
         </is>
       </c>
       <c r="B574">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C574">
         <v>5</v>
@@ -15263,7 +15277,7 @@
         </is>
       </c>
       <c r="B575">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C575">
         <v>5</v>
@@ -15288,7 +15302,7 @@
         </is>
       </c>
       <c r="B576">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C576">
         <v>5</v>
@@ -15313,7 +15327,7 @@
         </is>
       </c>
       <c r="B577">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C577">
         <v>5</v>
@@ -15338,7 +15352,7 @@
         </is>
       </c>
       <c r="B578">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C578">
         <v>5</v>
@@ -15363,7 +15377,7 @@
         </is>
       </c>
       <c r="B579">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C579">
         <v>5</v>
@@ -15388,7 +15402,7 @@
         </is>
       </c>
       <c r="B580">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C580">
         <v>5</v>
@@ -15413,7 +15427,7 @@
         </is>
       </c>
       <c r="B581">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C581">
         <v>5</v>
@@ -15438,7 +15452,7 @@
         </is>
       </c>
       <c r="B582">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C582">
         <v>5</v>
@@ -15463,7 +15477,7 @@
         </is>
       </c>
       <c r="B583">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C583">
         <v>5</v>
@@ -15488,7 +15502,7 @@
         </is>
       </c>
       <c r="B584">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C584">
         <v>5</v>
@@ -15513,7 +15527,7 @@
         </is>
       </c>
       <c r="B585">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C585">
         <v>5</v>
@@ -15538,7 +15552,7 @@
         </is>
       </c>
       <c r="B586">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C586">
         <v>5</v>
@@ -15563,7 +15577,7 @@
         </is>
       </c>
       <c r="B587">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C587">
         <v>5</v>
@@ -15588,7 +15602,7 @@
         </is>
       </c>
       <c r="B588">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C588">
         <v>5</v>
@@ -15613,7 +15627,7 @@
         </is>
       </c>
       <c r="B589">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C589">
         <v>5</v>
@@ -15638,7 +15652,7 @@
         </is>
       </c>
       <c r="B590">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C590">
         <v>5</v>
@@ -15663,7 +15677,7 @@
         </is>
       </c>
       <c r="B591">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C591">
         <v>5</v>
@@ -15688,7 +15702,7 @@
         </is>
       </c>
       <c r="B592">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C592">
         <v>5</v>
@@ -15713,7 +15727,7 @@
         </is>
       </c>
       <c r="B593">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C593">
         <v>5</v>
@@ -15738,7 +15752,7 @@
         </is>
       </c>
       <c r="B594">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C594">
         <v>5</v>
@@ -15763,7 +15777,7 @@
         </is>
       </c>
       <c r="B595">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C595">
         <v>5</v>
@@ -15788,7 +15802,7 @@
         </is>
       </c>
       <c r="B596">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C596">
         <v>5</v>
@@ -15813,7 +15827,7 @@
         </is>
       </c>
       <c r="B597">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C597">
         <v>5</v>
@@ -15838,7 +15852,7 @@
         </is>
       </c>
       <c r="B598">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C598">
         <v>5</v>
@@ -15863,7 +15877,7 @@
         </is>
       </c>
       <c r="B599">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C599">
         <v>5</v>
@@ -15888,7 +15902,7 @@
         </is>
       </c>
       <c r="B600">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C600">
         <v>5</v>
@@ -15913,7 +15927,7 @@
         </is>
       </c>
       <c r="B601">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C601">
         <v>5</v>
@@ -15938,7 +15952,7 @@
         </is>
       </c>
       <c r="B602">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C602">
         <v>5</v>
@@ -15963,7 +15977,7 @@
         </is>
       </c>
       <c r="B603">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C603">
         <v>5</v>
@@ -15988,7 +16002,7 @@
         </is>
       </c>
       <c r="B604">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C604">
         <v>5</v>
@@ -16013,7 +16027,7 @@
         </is>
       </c>
       <c r="B605">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C605">
         <v>5</v>
@@ -16038,7 +16052,7 @@
         </is>
       </c>
       <c r="B606">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C606">
         <v>5</v>
@@ -16063,7 +16077,7 @@
         </is>
       </c>
       <c r="B607">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C607">
         <v>5</v>
@@ -16088,7 +16102,7 @@
         </is>
       </c>
       <c r="B608">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C608">
         <v>5</v>
@@ -16113,7 +16127,7 @@
         </is>
       </c>
       <c r="B609">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C609">
         <v>5</v>
@@ -16138,7 +16152,7 @@
         </is>
       </c>
       <c r="B610">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C610">
         <v>5</v>
@@ -16163,7 +16177,7 @@
         </is>
       </c>
       <c r="B611">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C611">
         <v>5</v>
@@ -16188,7 +16202,7 @@
         </is>
       </c>
       <c r="B612">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C612">
         <v>5</v>
@@ -16213,7 +16227,7 @@
         </is>
       </c>
       <c r="B613">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C613">
         <v>5</v>
@@ -16238,7 +16252,7 @@
         </is>
       </c>
       <c r="B614">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C614">
         <v>5</v>
@@ -16263,7 +16277,7 @@
         </is>
       </c>
       <c r="B615">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C615">
         <v>5</v>
@@ -16288,7 +16302,7 @@
         </is>
       </c>
       <c r="B616">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C616">
         <v>5</v>
@@ -16313,7 +16327,7 @@
         </is>
       </c>
       <c r="B617">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C617">
         <v>5</v>
@@ -16338,7 +16352,7 @@
         </is>
       </c>
       <c r="B618">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C618">
         <v>5</v>
@@ -16363,7 +16377,7 @@
         </is>
       </c>
       <c r="B619">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C619">
         <v>5</v>
@@ -16388,7 +16402,7 @@
         </is>
       </c>
       <c r="B620">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C620">
         <v>5</v>
@@ -16413,7 +16427,7 @@
         </is>
       </c>
       <c r="B621">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C621">
         <v>5</v>
@@ -16438,7 +16452,7 @@
         </is>
       </c>
       <c r="B622">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C622">
         <v>5</v>
@@ -16463,7 +16477,7 @@
         </is>
       </c>
       <c r="B623">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C623">
         <v>5</v>
@@ -16488,7 +16502,7 @@
         </is>
       </c>
       <c r="B624">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C624">
         <v>5</v>
@@ -16513,7 +16527,7 @@
         </is>
       </c>
       <c r="B625">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C625">
         <v>5</v>
@@ -16538,7 +16552,7 @@
         </is>
       </c>
       <c r="B626">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C626">
         <v>5</v>
@@ -16563,7 +16577,7 @@
         </is>
       </c>
       <c r="B627">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C627">
         <v>5</v>
@@ -16588,7 +16602,7 @@
         </is>
       </c>
       <c r="B628">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C628">
         <v>5</v>
@@ -16613,7 +16627,7 @@
         </is>
       </c>
       <c r="B629">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C629">
         <v>5</v>
@@ -16638,7 +16652,7 @@
         </is>
       </c>
       <c r="B630">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C630">
         <v>5</v>
@@ -16663,7 +16677,7 @@
         </is>
       </c>
       <c r="B631">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C631">
         <v>5</v>
@@ -16688,7 +16702,7 @@
         </is>
       </c>
       <c r="B632">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C632">
         <v>5</v>
@@ -16713,7 +16727,7 @@
         </is>
       </c>
       <c r="B633">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C633">
         <v>5</v>
@@ -16738,7 +16752,7 @@
         </is>
       </c>
       <c r="B634">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C634">
         <v>5</v>
@@ -16763,7 +16777,7 @@
         </is>
       </c>
       <c r="B635">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C635">
         <v>5</v>
@@ -16788,7 +16802,7 @@
         </is>
       </c>
       <c r="B636">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C636">
         <v>5</v>
@@ -16813,7 +16827,7 @@
         </is>
       </c>
       <c r="B637">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C637">
         <v>5</v>
@@ -16838,7 +16852,7 @@
         </is>
       </c>
       <c r="B638">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C638">
         <v>5</v>
@@ -16863,7 +16877,7 @@
         </is>
       </c>
       <c r="B639">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C639">
         <v>5</v>
@@ -16888,7 +16902,7 @@
         </is>
       </c>
       <c r="B640">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C640">
         <v>5</v>
@@ -16913,7 +16927,7 @@
         </is>
       </c>
       <c r="B641">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C641">
         <v>5</v>
@@ -16938,7 +16952,7 @@
         </is>
       </c>
       <c r="B642">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C642">
         <v>5</v>
@@ -16963,7 +16977,7 @@
         </is>
       </c>
       <c r="B643">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C643">
         <v>5</v>
@@ -16988,7 +17002,7 @@
         </is>
       </c>
       <c r="B644">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C644">
         <v>5</v>
@@ -17013,7 +17027,7 @@
         </is>
       </c>
       <c r="B645">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C645">
         <v>5</v>
@@ -17038,7 +17052,7 @@
         </is>
       </c>
       <c r="B646">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C646">
         <v>5</v>
@@ -17063,7 +17077,7 @@
         </is>
       </c>
       <c r="B647">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C647">
         <v>5</v>
@@ -17088,7 +17102,7 @@
         </is>
       </c>
       <c r="B648">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C648">
         <v>5</v>
@@ -17113,7 +17127,7 @@
         </is>
       </c>
       <c r="B649">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C649">
         <v>5</v>
@@ -17138,7 +17152,7 @@
         </is>
       </c>
       <c r="B650">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C650">
         <v>5</v>
@@ -17163,7 +17177,7 @@
         </is>
       </c>
       <c r="B651">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C651">
         <v>5</v>
@@ -17188,7 +17202,7 @@
         </is>
       </c>
       <c r="B652">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C652">
         <v>5</v>
@@ -17213,7 +17227,7 @@
         </is>
       </c>
       <c r="B653">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C653">
         <v>5</v>
@@ -17238,7 +17252,7 @@
         </is>
       </c>
       <c r="B654">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C654">
         <v>5</v>
@@ -17263,7 +17277,7 @@
         </is>
       </c>
       <c r="B655">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C655">
         <v>5</v>
@@ -17288,7 +17302,7 @@
         </is>
       </c>
       <c r="B656">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C656">
         <v>5</v>
@@ -17313,7 +17327,7 @@
         </is>
       </c>
       <c r="B657">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C657">
         <v>5</v>
@@ -17338,7 +17352,7 @@
         </is>
       </c>
       <c r="B658">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C658">
         <v>5</v>
@@ -17363,7 +17377,7 @@
         </is>
       </c>
       <c r="B659">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C659">
         <v>5</v>
@@ -17388,7 +17402,7 @@
         </is>
       </c>
       <c r="B660">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C660">
         <v>5</v>
@@ -17413,7 +17427,7 @@
         </is>
       </c>
       <c r="B661">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C661">
         <v>5</v>
@@ -17438,7 +17452,7 @@
         </is>
       </c>
       <c r="B662">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C662">
         <v>5</v>
@@ -17463,7 +17477,7 @@
         </is>
       </c>
       <c r="B663">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C663">
         <v>5</v>
@@ -17488,7 +17502,7 @@
         </is>
       </c>
       <c r="B664">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C664">
         <v>5</v>
@@ -17513,7 +17527,7 @@
         </is>
       </c>
       <c r="B665">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C665">
         <v>5</v>
@@ -17538,7 +17552,7 @@
         </is>
       </c>
       <c r="B666">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C666">
         <v>5</v>
@@ -17563,7 +17577,7 @@
         </is>
       </c>
       <c r="B667">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C667">
         <v>5</v>
@@ -17588,7 +17602,7 @@
         </is>
       </c>
       <c r="B668">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C668">
         <v>5</v>
@@ -17613,7 +17627,7 @@
         </is>
       </c>
       <c r="B669">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C669">
         <v>5</v>
@@ -17638,7 +17652,7 @@
         </is>
       </c>
       <c r="B670">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C670">
         <v>5</v>
@@ -17663,7 +17677,7 @@
         </is>
       </c>
       <c r="B671">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C671">
         <v>5</v>
@@ -17688,7 +17702,7 @@
         </is>
       </c>
       <c r="B672">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C672">
         <v>5</v>
@@ -17713,7 +17727,7 @@
         </is>
       </c>
       <c r="B673">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C673">
         <v>5</v>
@@ -17738,7 +17752,7 @@
         </is>
       </c>
       <c r="B674">
-        <v>3</v>
+        <v>1998</v>
       </c>
       <c r="C674">
         <v>2</v>
@@ -17763,7 +17777,7 @@
         </is>
       </c>
       <c r="B675">
-        <v>4</v>
+        <v>1999</v>
       </c>
       <c r="C675">
         <v>2</v>
@@ -17788,7 +17802,7 @@
         </is>
       </c>
       <c r="B676">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="C676">
         <v>2</v>
@@ -17813,7 +17827,7 @@
         </is>
       </c>
       <c r="B677">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C677">
         <v>2</v>
@@ -17838,7 +17852,7 @@
         </is>
       </c>
       <c r="B678">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C678">
         <v>2</v>
@@ -17863,7 +17877,7 @@
         </is>
       </c>
       <c r="B679">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C679">
         <v>2</v>
@@ -17888,7 +17902,7 @@
         </is>
       </c>
       <c r="B680">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C680">
         <v>2</v>
@@ -17913,7 +17927,7 @@
         </is>
       </c>
       <c r="B681">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C681">
         <v>2</v>
@@ -17938,7 +17952,7 @@
         </is>
       </c>
       <c r="B682">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C682">
         <v>2</v>
@@ -17963,7 +17977,7 @@
         </is>
       </c>
       <c r="B683">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C683">
         <v>2</v>
@@ -17988,7 +18002,7 @@
         </is>
       </c>
       <c r="B684">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C684">
         <v>2</v>
@@ -18013,7 +18027,7 @@
         </is>
       </c>
       <c r="B685">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C685">
         <v>2</v>
@@ -18038,7 +18052,7 @@
         </is>
       </c>
       <c r="B686">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C686">
         <v>2</v>
@@ -18063,7 +18077,7 @@
         </is>
       </c>
       <c r="B687">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C687">
         <v>2</v>
@@ -18088,7 +18102,7 @@
         </is>
       </c>
       <c r="B688">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C688">
         <v>2</v>
@@ -18113,7 +18127,7 @@
         </is>
       </c>
       <c r="B689">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C689">
         <v>2</v>
@@ -18138,7 +18152,7 @@
         </is>
       </c>
       <c r="B690">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C690">
         <v>2</v>
@@ -18163,7 +18177,7 @@
         </is>
       </c>
       <c r="B691">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C691">
         <v>2</v>
@@ -18188,7 +18202,7 @@
         </is>
       </c>
       <c r="B692">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C692">
         <v>2</v>
@@ -18213,7 +18227,7 @@
         </is>
       </c>
       <c r="B693">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C693">
         <v>2</v>
@@ -18238,7 +18252,7 @@
         </is>
       </c>
       <c r="B694">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C694">
         <v>2</v>
@@ -18263,7 +18277,7 @@
         </is>
       </c>
       <c r="B695">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C695">
         <v>2</v>
@@ -18288,7 +18302,7 @@
         </is>
       </c>
       <c r="B696">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C696">
         <v>2</v>
@@ -18313,7 +18327,7 @@
         </is>
       </c>
       <c r="B697">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C697">
         <v>2</v>
@@ -18338,7 +18352,7 @@
         </is>
       </c>
       <c r="B698">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C698">
         <v>2</v>
@@ -18363,7 +18377,7 @@
         </is>
       </c>
       <c r="B699">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C699">
         <v>2</v>
@@ -18388,7 +18402,7 @@
         </is>
       </c>
       <c r="B700">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C700">
         <v>2</v>
@@ -18413,7 +18427,7 @@
         </is>
       </c>
       <c r="B701">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C701">
         <v>2</v>
@@ -18438,7 +18452,7 @@
         </is>
       </c>
       <c r="B702">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C702">
         <v>2</v>
@@ -18463,7 +18477,7 @@
         </is>
       </c>
       <c r="B703">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C703">
         <v>2</v>
@@ -18488,7 +18502,7 @@
         </is>
       </c>
       <c r="B704">
-        <v>4</v>
+        <v>1999</v>
       </c>
       <c r="C704">
         <v>3</v>
@@ -18513,7 +18527,7 @@
         </is>
       </c>
       <c r="B705">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="C705">
         <v>3</v>
@@ -18538,7 +18552,7 @@
         </is>
       </c>
       <c r="B706">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C706">
         <v>3</v>
@@ -18563,7 +18577,7 @@
         </is>
       </c>
       <c r="B707">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C707">
         <v>3</v>
@@ -18588,7 +18602,7 @@
         </is>
       </c>
       <c r="B708">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C708">
         <v>3</v>
@@ -18613,7 +18627,7 @@
         </is>
       </c>
       <c r="B709">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C709">
         <v>3</v>
@@ -18638,7 +18652,7 @@
         </is>
       </c>
       <c r="B710">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C710">
         <v>3</v>
@@ -18663,7 +18677,7 @@
         </is>
       </c>
       <c r="B711">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C711">
         <v>3</v>
@@ -18688,7 +18702,7 @@
         </is>
       </c>
       <c r="B712">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C712">
         <v>3</v>
@@ -18713,7 +18727,7 @@
         </is>
       </c>
       <c r="B713">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C713">
         <v>3</v>
@@ -18738,7 +18752,7 @@
         </is>
       </c>
       <c r="B714">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C714">
         <v>3</v>
@@ -18763,7 +18777,7 @@
         </is>
       </c>
       <c r="B715">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C715">
         <v>3</v>
@@ -18788,7 +18802,7 @@
         </is>
       </c>
       <c r="B716">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C716">
         <v>3</v>
@@ -18813,7 +18827,7 @@
         </is>
       </c>
       <c r="B717">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C717">
         <v>3</v>
@@ -18838,7 +18852,7 @@
         </is>
       </c>
       <c r="B718">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C718">
         <v>3</v>
@@ -18863,7 +18877,7 @@
         </is>
       </c>
       <c r="B719">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C719">
         <v>3</v>
@@ -18888,7 +18902,7 @@
         </is>
       </c>
       <c r="B720">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C720">
         <v>3</v>
@@ -18913,7 +18927,7 @@
         </is>
       </c>
       <c r="B721">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C721">
         <v>3</v>
@@ -18938,7 +18952,7 @@
         </is>
       </c>
       <c r="B722">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C722">
         <v>3</v>
@@ -18963,7 +18977,7 @@
         </is>
       </c>
       <c r="B723">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C723">
         <v>3</v>
@@ -18988,7 +19002,7 @@
         </is>
       </c>
       <c r="B724">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C724">
         <v>3</v>
@@ -19013,7 +19027,7 @@
         </is>
       </c>
       <c r="B725">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C725">
         <v>3</v>
@@ -19038,7 +19052,7 @@
         </is>
       </c>
       <c r="B726">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C726">
         <v>3</v>
@@ -19063,7 +19077,7 @@
         </is>
       </c>
       <c r="B727">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C727">
         <v>3</v>
@@ -19088,7 +19102,7 @@
         </is>
       </c>
       <c r="B728">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C728">
         <v>3</v>
@@ -19113,7 +19127,7 @@
         </is>
       </c>
       <c r="B729">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C729">
         <v>3</v>
@@ -19138,7 +19152,7 @@
         </is>
       </c>
       <c r="B730">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C730">
         <v>3</v>
@@ -19163,7 +19177,7 @@
         </is>
       </c>
       <c r="B731">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C731">
         <v>3</v>
@@ -19188,7 +19202,7 @@
         </is>
       </c>
       <c r="B732">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C732">
         <v>3</v>
@@ -19213,7 +19227,7 @@
         </is>
       </c>
       <c r="B733">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C733">
         <v>3</v>
@@ -19238,7 +19252,7 @@
         </is>
       </c>
       <c r="B734">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C734">
         <v>5</v>
@@ -19263,7 +19277,7 @@
         </is>
       </c>
       <c r="B735">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C735">
         <v>5</v>
@@ -19288,7 +19302,7 @@
         </is>
       </c>
       <c r="B736">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C736">
         <v>5</v>
@@ -19313,7 +19327,7 @@
         </is>
       </c>
       <c r="B737">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C737">
         <v>5</v>
@@ -19338,7 +19352,7 @@
         </is>
       </c>
       <c r="B738">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C738">
         <v>5</v>
@@ -19363,7 +19377,7 @@
         </is>
       </c>
       <c r="B739">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C739">
         <v>5</v>
@@ -19388,7 +19402,7 @@
         </is>
       </c>
       <c r="B740">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C740">
         <v>5</v>
@@ -19413,7 +19427,7 @@
         </is>
       </c>
       <c r="B741">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C741">
         <v>5</v>
@@ -19438,7 +19452,7 @@
         </is>
       </c>
       <c r="B742">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C742">
         <v>5</v>
@@ -19463,7 +19477,7 @@
         </is>
       </c>
       <c r="B743">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C743">
         <v>5</v>
@@ -19488,7 +19502,7 @@
         </is>
       </c>
       <c r="B744">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C744">
         <v>5</v>
@@ -19513,7 +19527,7 @@
         </is>
       </c>
       <c r="B745">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C745">
         <v>5</v>
@@ -19538,7 +19552,7 @@
         </is>
       </c>
       <c r="B746">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C746">
         <v>5</v>
@@ -19563,7 +19577,7 @@
         </is>
       </c>
       <c r="B747">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C747">
         <v>5</v>
@@ -19588,7 +19602,7 @@
         </is>
       </c>
       <c r="B748">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C748">
         <v>5</v>
@@ -19613,7 +19627,7 @@
         </is>
       </c>
       <c r="B749">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C749">
         <v>5</v>
@@ -19638,7 +19652,7 @@
         </is>
       </c>
       <c r="B750">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C750">
         <v>5</v>
@@ -19663,7 +19677,7 @@
         </is>
       </c>
       <c r="B751">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C751">
         <v>5</v>
@@ -19688,7 +19702,7 @@
         </is>
       </c>
       <c r="B752">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C752">
         <v>5</v>
@@ -19713,7 +19727,7 @@
         </is>
       </c>
       <c r="B753">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C753">
         <v>5</v>
@@ -19738,7 +19752,7 @@
         </is>
       </c>
       <c r="B754">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C754">
         <v>5</v>
@@ -19763,7 +19777,7 @@
         </is>
       </c>
       <c r="B755">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C755">
         <v>5</v>
@@ -19788,7 +19802,7 @@
         </is>
       </c>
       <c r="B756">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C756">
         <v>5</v>
@@ -19813,7 +19827,7 @@
         </is>
       </c>
       <c r="B757">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C757">
         <v>5</v>
@@ -19838,7 +19852,7 @@
         </is>
       </c>
       <c r="B758">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C758">
         <v>5</v>
@@ -19863,7 +19877,7 @@
         </is>
       </c>
       <c r="B759">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C759">
         <v>5</v>
@@ -19888,7 +19902,7 @@
         </is>
       </c>
       <c r="B760">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C760">
         <v>5</v>
@@ -19913,7 +19927,7 @@
         </is>
       </c>
       <c r="B761">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C761">
         <v>5</v>
@@ -19938,7 +19952,7 @@
         </is>
       </c>
       <c r="B762">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C762">
         <v>14</v>
@@ -19963,7 +19977,7 @@
         </is>
       </c>
       <c r="B763">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C763">
         <v>14</v>
@@ -19988,7 +20002,7 @@
         </is>
       </c>
       <c r="B764">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C764">
         <v>14</v>
@@ -20013,7 +20027,7 @@
         </is>
       </c>
       <c r="B765">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C765">
         <v>14</v>
@@ -20038,7 +20052,7 @@
         </is>
       </c>
       <c r="B766">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C766">
         <v>14</v>
@@ -20063,7 +20077,7 @@
         </is>
       </c>
       <c r="B767">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C767">
         <v>14</v>
@@ -20088,7 +20102,7 @@
         </is>
       </c>
       <c r="B768">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C768">
         <v>14</v>
@@ -20113,7 +20127,7 @@
         </is>
       </c>
       <c r="B769">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C769">
         <v>14</v>
@@ -20138,7 +20152,7 @@
         </is>
       </c>
       <c r="B770">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C770">
         <v>14</v>
@@ -20163,7 +20177,7 @@
         </is>
       </c>
       <c r="B771">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C771">
         <v>14</v>
@@ -20188,7 +20202,7 @@
         </is>
       </c>
       <c r="B772">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C772">
         <v>14</v>
@@ -20213,7 +20227,7 @@
         </is>
       </c>
       <c r="B773">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C773">
         <v>14</v>
@@ -20238,7 +20252,7 @@
         </is>
       </c>
       <c r="B774">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C774">
         <v>14</v>
@@ -20263,7 +20277,7 @@
         </is>
       </c>
       <c r="B775">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C775">
         <v>14</v>
@@ -20288,7 +20302,7 @@
         </is>
       </c>
       <c r="B776">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C776">
         <v>14</v>
@@ -20313,7 +20327,7 @@
         </is>
       </c>
       <c r="B777">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C777">
         <v>11</v>
@@ -20338,7 +20352,7 @@
         </is>
       </c>
       <c r="B778">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C778">
         <v>11</v>
@@ -20363,7 +20377,7 @@
         </is>
       </c>
       <c r="B779">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C779">
         <v>11</v>
@@ -20388,7 +20402,7 @@
         </is>
       </c>
       <c r="B780">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C780">
         <v>11</v>
@@ -20413,7 +20427,7 @@
         </is>
       </c>
       <c r="B781">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C781">
         <v>11</v>
@@ -20438,7 +20452,7 @@
         </is>
       </c>
       <c r="B782">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C782">
         <v>11</v>
@@ -20463,7 +20477,7 @@
         </is>
       </c>
       <c r="B783">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C783">
         <v>11</v>
@@ -20488,7 +20502,7 @@
         </is>
       </c>
       <c r="B784">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C784">
         <v>11</v>
@@ -20513,7 +20527,7 @@
         </is>
       </c>
       <c r="B785">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C785">
         <v>11</v>
@@ -20538,7 +20552,7 @@
         </is>
       </c>
       <c r="B786">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C786">
         <v>11</v>
@@ -20563,7 +20577,7 @@
         </is>
       </c>
       <c r="B787">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C787">
         <v>11</v>
@@ -20588,7 +20602,7 @@
         </is>
       </c>
       <c r="B788">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C788">
         <v>11</v>
@@ -20613,7 +20627,7 @@
         </is>
       </c>
       <c r="B789">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C789">
         <v>11</v>
@@ -20638,7 +20652,7 @@
         </is>
       </c>
       <c r="B790">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C790">
         <v>11</v>
@@ -20663,7 +20677,7 @@
         </is>
       </c>
       <c r="B791">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C791">
         <v>11</v>
@@ -20688,7 +20702,7 @@
         </is>
       </c>
       <c r="B792">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C792">
         <v>11</v>
@@ -20713,7 +20727,7 @@
         </is>
       </c>
       <c r="B793">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C793">
         <v>11</v>
@@ -20738,7 +20752,7 @@
         </is>
       </c>
       <c r="B794">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C794">
         <v>11</v>
@@ -20763,7 +20777,7 @@
         </is>
       </c>
       <c r="B795">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C795">
         <v>11</v>
@@ -20788,7 +20802,7 @@
         </is>
       </c>
       <c r="B796">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C796">
         <v>11</v>
@@ -20813,7 +20827,7 @@
         </is>
       </c>
       <c r="B797">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C797">
         <v>11</v>
@@ -20838,7 +20852,7 @@
         </is>
       </c>
       <c r="B798">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C798">
         <v>11</v>
@@ -20863,7 +20877,7 @@
         </is>
       </c>
       <c r="B799">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C799">
         <v>11</v>
@@ -20888,7 +20902,7 @@
         </is>
       </c>
       <c r="B800">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C800">
         <v>11</v>
@@ -20913,7 +20927,7 @@
         </is>
       </c>
       <c r="B801">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C801">
         <v>11</v>
@@ -20938,7 +20952,7 @@
         </is>
       </c>
       <c r="B802">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C802">
         <v>11</v>
@@ -20963,7 +20977,7 @@
         </is>
       </c>
       <c r="B803">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C803">
         <v>11</v>
@@ -20988,7 +21002,7 @@
         </is>
       </c>
       <c r="B804">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C804">
         <v>11</v>
@@ -21013,7 +21027,7 @@
         </is>
       </c>
       <c r="B805">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C805">
         <v>11</v>
@@ -21038,7 +21052,7 @@
         </is>
       </c>
       <c r="B806">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C806">
         <v>11</v>
@@ -21063,7 +21077,7 @@
         </is>
       </c>
       <c r="B807">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C807">
         <v>11</v>
@@ -21088,7 +21102,7 @@
         </is>
       </c>
       <c r="B808">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C808">
         <v>11</v>
@@ -21113,7 +21127,7 @@
         </is>
       </c>
       <c r="B809">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C809">
         <v>11</v>
@@ -21138,7 +21152,7 @@
         </is>
       </c>
       <c r="B810">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C810">
         <v>11</v>
@@ -21163,7 +21177,7 @@
         </is>
       </c>
       <c r="B811">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C811">
         <v>11</v>
@@ -21188,7 +21202,7 @@
         </is>
       </c>
       <c r="B812">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C812">
         <v>11</v>
@@ -21213,7 +21227,7 @@
         </is>
       </c>
       <c r="B813">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C813">
         <v>11</v>
@@ -21238,7 +21252,7 @@
         </is>
       </c>
       <c r="B814">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C814">
         <v>11</v>
@@ -21263,7 +21277,7 @@
         </is>
       </c>
       <c r="B815">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C815">
         <v>11</v>
@@ -21288,7 +21302,7 @@
         </is>
       </c>
       <c r="B816">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C816">
         <v>11</v>
@@ -21313,7 +21327,7 @@
         </is>
       </c>
       <c r="B817">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C817">
         <v>11</v>
@@ -21338,7 +21352,7 @@
         </is>
       </c>
       <c r="B818">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C818">
         <v>11</v>
@@ -21363,7 +21377,7 @@
         </is>
       </c>
       <c r="B819">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C819">
         <v>11</v>
@@ -21388,7 +21402,7 @@
         </is>
       </c>
       <c r="B820">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C820">
         <v>11</v>
@@ -21413,7 +21427,7 @@
         </is>
       </c>
       <c r="B821">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C821">
         <v>11</v>
@@ -21438,7 +21452,7 @@
         </is>
       </c>
       <c r="B822">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C822">
         <v>11</v>
@@ -21463,7 +21477,7 @@
         </is>
       </c>
       <c r="B823">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C823">
         <v>11</v>
@@ -21488,7 +21502,7 @@
         </is>
       </c>
       <c r="B824">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C824">
         <v>11</v>
@@ -21513,7 +21527,7 @@
         </is>
       </c>
       <c r="B825">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C825">
         <v>11</v>
@@ -21538,7 +21552,7 @@
         </is>
       </c>
       <c r="B826">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C826">
         <v>11</v>
@@ -21563,7 +21577,7 @@
         </is>
       </c>
       <c r="B827">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C827">
         <v>11</v>
@@ -21588,7 +21602,7 @@
         </is>
       </c>
       <c r="B828">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C828">
         <v>11</v>
@@ -21613,7 +21627,7 @@
         </is>
       </c>
       <c r="B829">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C829">
         <v>11</v>
@@ -21638,7 +21652,7 @@
         </is>
       </c>
       <c r="B830">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C830">
         <v>11</v>
@@ -21663,7 +21677,7 @@
         </is>
       </c>
       <c r="B831">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C831">
         <v>11</v>
@@ -21688,7 +21702,7 @@
         </is>
       </c>
       <c r="B832">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C832">
         <v>11</v>
@@ -21713,7 +21727,7 @@
         </is>
       </c>
       <c r="B833">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C833">
         <v>11</v>
@@ -21738,7 +21752,7 @@
         </is>
       </c>
       <c r="B834">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C834">
         <v>11</v>
@@ -21763,7 +21777,7 @@
         </is>
       </c>
       <c r="B835">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C835">
         <v>11</v>
@@ -21788,7 +21802,7 @@
         </is>
       </c>
       <c r="B836">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C836">
         <v>11</v>
@@ -21813,7 +21827,7 @@
         </is>
       </c>
       <c r="B837">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C837">
         <v>11</v>
@@ -21838,7 +21852,7 @@
         </is>
       </c>
       <c r="B838">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C838">
         <v>11</v>
@@ -21863,7 +21877,7 @@
         </is>
       </c>
       <c r="B839">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C839">
         <v>11</v>
@@ -21888,7 +21902,7 @@
         </is>
       </c>
       <c r="B840">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C840">
         <v>11</v>
@@ -21913,7 +21927,7 @@
         </is>
       </c>
       <c r="B841">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C841">
         <v>11</v>
@@ -21938,7 +21952,7 @@
         </is>
       </c>
       <c r="B842">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C842">
         <v>11</v>
@@ -21959,8 +21973,8 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -22384,7 +22398,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -22428,8 +22442,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/tests/testthat/fixtures/example.xlsx
+++ b/tests/testthat/fixtures/example.xlsx
@@ -386,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="100.711"/>
@@ -521,250 +521,243 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  seed              optional random seed for reproducibility</t>
+          <t xml:space="preserve">  Add optional settings as extra rows when needed, e.g. seed, warmup, cores,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  warmup            optional warmup iterations per chain</t>
+          <t xml:space="preserve">  thin, adapt_delta, max_treedepth, df, or dose_schedule (dose ages, e.g. 1, 4).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Leave seed/warmup blank to use the model defaults.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>observations sheet -- one row per sampled count:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>observations sheet -- one row per sampled count:</t>
+          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          the location of this count (must match a Location in the locations sheet)</t>
+          <t xml:space="preserve">  Observation Year  timing of the observation</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age this count covers</t>
+          <t xml:space="preserve">  Oldest age        oldest age covered; for one age, repeat Youngest age or leave blank</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age this count covers (put the same age in both for a single age)</t>
+          <t xml:space="preserve">  Dose              which dose this count is for (1 = first dose, 2 = second, ...)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              which dose this count is for: 1 or 2</t>
+          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Vaccinated        how many were found vaccinated</t>
+          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sampled           how many were sampled (Vaccinated must be &lt;= Sampled)</t>
+          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Censored          optional; leave blank, or put 1 for a right-censored observation</t>
+          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A count covering several ages is split evenly across them, and the cohort of each age</t>
+          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is derived as Observation Year - age (a snapshot in time). If you prefer,</t>
+          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  you may use a single 'Age' column instead of the two age columns.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>locations sheet -- your location hierarchy, written as a tree:</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>locations sheet -- your location hierarchy, written as a tree:</t>
+          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          a unique name for the location (you choose the names)</t>
+          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Parent location   the name of this location's parent (must be another Location in this sheet)</t>
+          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  IMPORTANT: there must be exactly ONE root -- the single top location whose Parent location</t>
+          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  is left BLANK. Every other location must name its parent, and the parents must chain up to</t>
+          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  that one root (no loops, no second root). This is the most common thing to get wrong.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>target sheet -- the populations to predict coverage for (required):</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>target sheet -- the populations to predict coverage for (required):</t>
+          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Location          one or more locations to predict, ';'-separated</t>
+          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Youngest age      youngest age to predict</t>
+          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Oldest age        oldest age to predict</t>
+          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Dose              optional; leave blank to default to the final dose</t>
+          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Label             optional; free-text label echoed into the results</t>
+          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A Location-only row (year/ages/dose left blank) inherits those from the row above it.</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>Check from R: imuRUN::run_fit('yourfile.xlsx', dryrun = TRUE)</t>
+          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Fit from R:   imuRUN::run_fit('yourfile.xlsx')</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>If you installed the optional command wrapper, 'imurun yourfile.xlsx' also works.</t>
         </is>
@@ -779,12 +772,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="5.711"/>
-    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="40.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="26.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,40 +828,6 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>Number of chains</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Optional random seed for reproducibility</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>warmup</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Optional warmup iterations per chain</t>
         </is>
       </c>
     </row>
@@ -938,7 +897,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C2">
         <v>5</v>
@@ -963,7 +922,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -988,7 +947,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -1013,7 +972,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1038,7 +997,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1063,7 +1022,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1088,7 +1047,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -1113,7 +1072,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1138,7 +1097,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1163,7 +1122,7 @@
         </is>
       </c>
       <c r="B11">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1188,7 +1147,7 @@
         </is>
       </c>
       <c r="B12">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -1213,7 +1172,7 @@
         </is>
       </c>
       <c r="B13">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -1238,7 +1197,7 @@
         </is>
       </c>
       <c r="B14">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -1263,7 +1222,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -1288,7 +1247,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1313,7 +1272,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C17">
         <v>5</v>
@@ -1338,7 +1297,7 @@
         </is>
       </c>
       <c r="B18">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C18">
         <v>5</v>
@@ -1363,7 +1322,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C19">
         <v>5</v>
@@ -1388,7 +1347,7 @@
         </is>
       </c>
       <c r="B20">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C20">
         <v>5</v>
@@ -1413,7 +1372,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C21">
         <v>5</v>
@@ -1438,7 +1397,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C22">
         <v>5</v>
@@ -1463,7 +1422,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C23">
         <v>5</v>
@@ -1488,7 +1447,7 @@
         </is>
       </c>
       <c r="B24">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C24">
         <v>5</v>
@@ -1513,7 +1472,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -1538,7 +1497,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1563,7 +1522,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C27">
         <v>5</v>
@@ -1588,7 +1547,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C28">
         <v>5</v>
@@ -1613,7 +1572,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1638,7 +1597,7 @@
         </is>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C30">
         <v>5</v>
@@ -1663,7 +1622,7 @@
         </is>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C31">
         <v>5</v>
@@ -1688,7 +1647,7 @@
         </is>
       </c>
       <c r="B32">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C32">
         <v>5</v>
@@ -1713,7 +1672,7 @@
         </is>
       </c>
       <c r="B33">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -1738,7 +1697,7 @@
         </is>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C34">
         <v>5</v>
@@ -1763,7 +1722,7 @@
         </is>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C35">
         <v>5</v>
@@ -1788,7 +1747,7 @@
         </is>
       </c>
       <c r="B36">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -1813,7 +1772,7 @@
         </is>
       </c>
       <c r="B37">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -1838,7 +1797,7 @@
         </is>
       </c>
       <c r="B38">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -1863,7 +1822,7 @@
         </is>
       </c>
       <c r="B39">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C39">
         <v>5</v>
@@ -1888,7 +1847,7 @@
         </is>
       </c>
       <c r="B40">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C40">
         <v>5</v>
@@ -1913,7 +1872,7 @@
         </is>
       </c>
       <c r="B41">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -1938,7 +1897,7 @@
         </is>
       </c>
       <c r="B42">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -1963,7 +1922,7 @@
         </is>
       </c>
       <c r="B43">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -1988,7 +1947,7 @@
         </is>
       </c>
       <c r="B44">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -2013,7 +1972,7 @@
         </is>
       </c>
       <c r="B45">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2038,7 +1997,7 @@
         </is>
       </c>
       <c r="B46">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -2063,7 +2022,7 @@
         </is>
       </c>
       <c r="B47">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -2088,7 +2047,7 @@
         </is>
       </c>
       <c r="B48">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -2113,7 +2072,7 @@
         </is>
       </c>
       <c r="B49">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -2138,7 +2097,7 @@
         </is>
       </c>
       <c r="B50">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C50">
         <v>5</v>
@@ -2163,7 +2122,7 @@
         </is>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C51">
         <v>5</v>
@@ -2188,7 +2147,7 @@
         </is>
       </c>
       <c r="B52">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C52">
         <v>5</v>
@@ -2213,7 +2172,7 @@
         </is>
       </c>
       <c r="B53">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C53">
         <v>5</v>
@@ -2238,7 +2197,7 @@
         </is>
       </c>
       <c r="B54">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C54">
         <v>5</v>
@@ -2263,7 +2222,7 @@
         </is>
       </c>
       <c r="B55">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C55">
         <v>5</v>
@@ -2288,7 +2247,7 @@
         </is>
       </c>
       <c r="B56">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C56">
         <v>5</v>
@@ -2313,7 +2272,7 @@
         </is>
       </c>
       <c r="B57">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C57">
         <v>5</v>
@@ -2338,7 +2297,7 @@
         </is>
       </c>
       <c r="B58">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C58">
         <v>5</v>
@@ -2363,7 +2322,7 @@
         </is>
       </c>
       <c r="B59">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C59">
         <v>5</v>
@@ -2388,7 +2347,7 @@
         </is>
       </c>
       <c r="B60">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2413,7 +2372,7 @@
         </is>
       </c>
       <c r="B61">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C61">
         <v>5</v>
@@ -2438,7 +2397,7 @@
         </is>
       </c>
       <c r="B62">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C62">
         <v>5</v>
@@ -2463,7 +2422,7 @@
         </is>
       </c>
       <c r="B63">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -2488,7 +2447,7 @@
         </is>
       </c>
       <c r="B64">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C64">
         <v>5</v>
@@ -2513,7 +2472,7 @@
         </is>
       </c>
       <c r="B65">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C65">
         <v>5</v>
@@ -2538,7 +2497,7 @@
         </is>
       </c>
       <c r="B66">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -2563,7 +2522,7 @@
         </is>
       </c>
       <c r="B67">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C67">
         <v>5</v>
@@ -2588,7 +2547,7 @@
         </is>
       </c>
       <c r="B68">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C68">
         <v>5</v>
@@ -2613,7 +2572,7 @@
         </is>
       </c>
       <c r="B69">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C69">
         <v>5</v>
@@ -2638,7 +2597,7 @@
         </is>
       </c>
       <c r="B70">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C70">
         <v>5</v>
@@ -2663,7 +2622,7 @@
         </is>
       </c>
       <c r="B71">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C71">
         <v>5</v>
@@ -2688,7 +2647,7 @@
         </is>
       </c>
       <c r="B72">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C72">
         <v>5</v>
@@ -2713,7 +2672,7 @@
         </is>
       </c>
       <c r="B73">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C73">
         <v>5</v>
@@ -2738,7 +2697,7 @@
         </is>
       </c>
       <c r="B74">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -2763,7 +2722,7 @@
         </is>
       </c>
       <c r="B75">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C75">
         <v>5</v>
@@ -2788,7 +2747,7 @@
         </is>
       </c>
       <c r="B76">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C76">
         <v>5</v>
@@ -2813,7 +2772,7 @@
         </is>
       </c>
       <c r="B77">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C77">
         <v>5</v>
@@ -2838,7 +2797,7 @@
         </is>
       </c>
       <c r="B78">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C78">
         <v>5</v>
@@ -2863,7 +2822,7 @@
         </is>
       </c>
       <c r="B79">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C79">
         <v>5</v>
@@ -2888,7 +2847,7 @@
         </is>
       </c>
       <c r="B80">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C80">
         <v>5</v>
@@ -2913,7 +2872,7 @@
         </is>
       </c>
       <c r="B81">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C81">
         <v>5</v>
@@ -2938,7 +2897,7 @@
         </is>
       </c>
       <c r="B82">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C82">
         <v>5</v>
@@ -2963,7 +2922,7 @@
         </is>
       </c>
       <c r="B83">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C83">
         <v>5</v>
@@ -2988,7 +2947,7 @@
         </is>
       </c>
       <c r="B84">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C84">
         <v>5</v>
@@ -3013,7 +2972,7 @@
         </is>
       </c>
       <c r="B85">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C85">
         <v>5</v>
@@ -3038,7 +2997,7 @@
         </is>
       </c>
       <c r="B86">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C86">
         <v>5</v>
@@ -3063,7 +3022,7 @@
         </is>
       </c>
       <c r="B87">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C87">
         <v>5</v>
@@ -3088,7 +3047,7 @@
         </is>
       </c>
       <c r="B88">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C88">
         <v>5</v>
@@ -3113,7 +3072,7 @@
         </is>
       </c>
       <c r="B89">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C89">
         <v>5</v>
@@ -3138,7 +3097,7 @@
         </is>
       </c>
       <c r="B90">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C90">
         <v>5</v>
@@ -3163,7 +3122,7 @@
         </is>
       </c>
       <c r="B91">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C91">
         <v>5</v>
@@ -3188,7 +3147,7 @@
         </is>
       </c>
       <c r="B92">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C92">
         <v>5</v>
@@ -3213,7 +3172,7 @@
         </is>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C93">
         <v>5</v>
@@ -3238,7 +3197,7 @@
         </is>
       </c>
       <c r="B94">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C94">
         <v>5</v>
@@ -3263,7 +3222,7 @@
         </is>
       </c>
       <c r="B95">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C95">
         <v>5</v>
@@ -3288,7 +3247,7 @@
         </is>
       </c>
       <c r="B96">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C96">
         <v>5</v>
@@ -3313,7 +3272,7 @@
         </is>
       </c>
       <c r="B97">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C97">
         <v>5</v>
@@ -3338,7 +3297,7 @@
         </is>
       </c>
       <c r="B98">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C98">
         <v>5</v>
@@ -3363,7 +3322,7 @@
         </is>
       </c>
       <c r="B99">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C99">
         <v>5</v>
@@ -3388,7 +3347,7 @@
         </is>
       </c>
       <c r="B100">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C100">
         <v>5</v>
@@ -3413,7 +3372,7 @@
         </is>
       </c>
       <c r="B101">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C101">
         <v>5</v>
@@ -3438,7 +3397,7 @@
         </is>
       </c>
       <c r="B102">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C102">
         <v>5</v>
@@ -3463,7 +3422,7 @@
         </is>
       </c>
       <c r="B103">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C103">
         <v>5</v>
@@ -3488,7 +3447,7 @@
         </is>
       </c>
       <c r="B104">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C104">
         <v>5</v>
@@ -3513,7 +3472,7 @@
         </is>
       </c>
       <c r="B105">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C105">
         <v>5</v>
@@ -3538,7 +3497,7 @@
         </is>
       </c>
       <c r="B106">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C106">
         <v>5</v>
@@ -3563,7 +3522,7 @@
         </is>
       </c>
       <c r="B107">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C107">
         <v>5</v>
@@ -3588,7 +3547,7 @@
         </is>
       </c>
       <c r="B108">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C108">
         <v>5</v>
@@ -3613,7 +3572,7 @@
         </is>
       </c>
       <c r="B109">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C109">
         <v>5</v>
@@ -3638,7 +3597,7 @@
         </is>
       </c>
       <c r="B110">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C110">
         <v>5</v>
@@ -3663,7 +3622,7 @@
         </is>
       </c>
       <c r="B111">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C111">
         <v>5</v>
@@ -3688,7 +3647,7 @@
         </is>
       </c>
       <c r="B112">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C112">
         <v>5</v>
@@ -3713,7 +3672,7 @@
         </is>
       </c>
       <c r="B113">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C113">
         <v>5</v>
@@ -3738,7 +3697,7 @@
         </is>
       </c>
       <c r="B114">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C114">
         <v>5</v>
@@ -3763,7 +3722,7 @@
         </is>
       </c>
       <c r="B115">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C115">
         <v>5</v>
@@ -3788,7 +3747,7 @@
         </is>
       </c>
       <c r="B116">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C116">
         <v>5</v>
@@ -3813,7 +3772,7 @@
         </is>
       </c>
       <c r="B117">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C117">
         <v>5</v>
@@ -3838,7 +3797,7 @@
         </is>
       </c>
       <c r="B118">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C118">
         <v>5</v>
@@ -3863,7 +3822,7 @@
         </is>
       </c>
       <c r="B119">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C119">
         <v>5</v>
@@ -3888,7 +3847,7 @@
         </is>
       </c>
       <c r="B120">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C120">
         <v>5</v>
@@ -3913,7 +3872,7 @@
         </is>
       </c>
       <c r="B121">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C121">
         <v>5</v>
@@ -3938,7 +3897,7 @@
         </is>
       </c>
       <c r="B122">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C122">
         <v>5</v>
@@ -3963,7 +3922,7 @@
         </is>
       </c>
       <c r="B123">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C123">
         <v>5</v>
@@ -3988,7 +3947,7 @@
         </is>
       </c>
       <c r="B124">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C124">
         <v>5</v>
@@ -4013,7 +3972,7 @@
         </is>
       </c>
       <c r="B125">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C125">
         <v>5</v>
@@ -4038,7 +3997,7 @@
         </is>
       </c>
       <c r="B126">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C126">
         <v>5</v>
@@ -4063,7 +4022,7 @@
         </is>
       </c>
       <c r="B127">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C127">
         <v>5</v>
@@ -4088,7 +4047,7 @@
         </is>
       </c>
       <c r="B128">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C128">
         <v>5</v>
@@ -4113,7 +4072,7 @@
         </is>
       </c>
       <c r="B129">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C129">
         <v>5</v>
@@ -4138,7 +4097,7 @@
         </is>
       </c>
       <c r="B130">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C130">
         <v>5</v>
@@ -4163,7 +4122,7 @@
         </is>
       </c>
       <c r="B131">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C131">
         <v>5</v>
@@ -4188,7 +4147,7 @@
         </is>
       </c>
       <c r="B132">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C132">
         <v>5</v>
@@ -4213,7 +4172,7 @@
         </is>
       </c>
       <c r="B133">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C133">
         <v>5</v>
@@ -4238,7 +4197,7 @@
         </is>
       </c>
       <c r="B134">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C134">
         <v>5</v>
@@ -4263,7 +4222,7 @@
         </is>
       </c>
       <c r="B135">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C135">
         <v>5</v>
@@ -4288,7 +4247,7 @@
         </is>
       </c>
       <c r="B136">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C136">
         <v>5</v>
@@ -4313,7 +4272,7 @@
         </is>
       </c>
       <c r="B137">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C137">
         <v>5</v>
@@ -4338,7 +4297,7 @@
         </is>
       </c>
       <c r="B138">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C138">
         <v>5</v>
@@ -4363,7 +4322,7 @@
         </is>
       </c>
       <c r="B139">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C139">
         <v>5</v>
@@ -4388,7 +4347,7 @@
         </is>
       </c>
       <c r="B140">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C140">
         <v>5</v>
@@ -4413,7 +4372,7 @@
         </is>
       </c>
       <c r="B141">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C141">
         <v>5</v>
@@ -4438,7 +4397,7 @@
         </is>
       </c>
       <c r="B142">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C142">
         <v>5</v>
@@ -4463,7 +4422,7 @@
         </is>
       </c>
       <c r="B143">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C143">
         <v>5</v>
@@ -4488,7 +4447,7 @@
         </is>
       </c>
       <c r="B144">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C144">
         <v>5</v>
@@ -4513,7 +4472,7 @@
         </is>
       </c>
       <c r="B145">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C145">
         <v>5</v>
@@ -4538,7 +4497,7 @@
         </is>
       </c>
       <c r="B146">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C146">
         <v>5</v>
@@ -4563,7 +4522,7 @@
         </is>
       </c>
       <c r="B147">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C147">
         <v>5</v>
@@ -4588,7 +4547,7 @@
         </is>
       </c>
       <c r="B148">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C148">
         <v>5</v>
@@ -4613,7 +4572,7 @@
         </is>
       </c>
       <c r="B149">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C149">
         <v>5</v>
@@ -4638,7 +4597,7 @@
         </is>
       </c>
       <c r="B150">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C150">
         <v>5</v>
@@ -4663,7 +4622,7 @@
         </is>
       </c>
       <c r="B151">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C151">
         <v>5</v>
@@ -4688,7 +4647,7 @@
         </is>
       </c>
       <c r="B152">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C152">
         <v>5</v>
@@ -4713,7 +4672,7 @@
         </is>
       </c>
       <c r="B153">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C153">
         <v>5</v>
@@ -4738,7 +4697,7 @@
         </is>
       </c>
       <c r="B154">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C154">
         <v>5</v>
@@ -4763,7 +4722,7 @@
         </is>
       </c>
       <c r="B155">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C155">
         <v>5</v>
@@ -4788,7 +4747,7 @@
         </is>
       </c>
       <c r="B156">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C156">
         <v>5</v>
@@ -4813,7 +4772,7 @@
         </is>
       </c>
       <c r="B157">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C157">
         <v>5</v>
@@ -4838,7 +4797,7 @@
         </is>
       </c>
       <c r="B158">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C158">
         <v>5</v>
@@ -4863,7 +4822,7 @@
         </is>
       </c>
       <c r="B159">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C159">
         <v>5</v>
@@ -4888,7 +4847,7 @@
         </is>
       </c>
       <c r="B160">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C160">
         <v>5</v>
@@ -4913,7 +4872,7 @@
         </is>
       </c>
       <c r="B161">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C161">
         <v>5</v>
@@ -4938,7 +4897,7 @@
         </is>
       </c>
       <c r="B162">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C162">
         <v>5</v>
@@ -4963,7 +4922,7 @@
         </is>
       </c>
       <c r="B163">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C163">
         <v>5</v>
@@ -4988,7 +4947,7 @@
         </is>
       </c>
       <c r="B164">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C164">
         <v>5</v>
@@ -5013,7 +4972,7 @@
         </is>
       </c>
       <c r="B165">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C165">
         <v>5</v>
@@ -5038,7 +4997,7 @@
         </is>
       </c>
       <c r="B166">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C166">
         <v>5</v>
@@ -5063,7 +5022,7 @@
         </is>
       </c>
       <c r="B167">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C167">
         <v>5</v>
@@ -5088,7 +5047,7 @@
         </is>
       </c>
       <c r="B168">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C168">
         <v>5</v>
@@ -5113,7 +5072,7 @@
         </is>
       </c>
       <c r="B169">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C169">
         <v>5</v>
@@ -5138,7 +5097,7 @@
         </is>
       </c>
       <c r="B170">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C170">
         <v>5</v>
@@ -5163,7 +5122,7 @@
         </is>
       </c>
       <c r="B171">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C171">
         <v>5</v>
@@ -5188,7 +5147,7 @@
         </is>
       </c>
       <c r="B172">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C172">
         <v>5</v>
@@ -5213,7 +5172,7 @@
         </is>
       </c>
       <c r="B173">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C173">
         <v>5</v>
@@ -5238,7 +5197,7 @@
         </is>
       </c>
       <c r="B174">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C174">
         <v>5</v>
@@ -5263,7 +5222,7 @@
         </is>
       </c>
       <c r="B175">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C175">
         <v>5</v>
@@ -5288,7 +5247,7 @@
         </is>
       </c>
       <c r="B176">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C176">
         <v>5</v>
@@ -5313,7 +5272,7 @@
         </is>
       </c>
       <c r="B177">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C177">
         <v>5</v>
@@ -5338,7 +5297,7 @@
         </is>
       </c>
       <c r="B178">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C178">
         <v>5</v>
@@ -5363,7 +5322,7 @@
         </is>
       </c>
       <c r="B179">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C179">
         <v>5</v>
@@ -5388,7 +5347,7 @@
         </is>
       </c>
       <c r="B180">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C180">
         <v>5</v>
@@ -5413,7 +5372,7 @@
         </is>
       </c>
       <c r="B181">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C181">
         <v>5</v>
@@ -5438,7 +5397,7 @@
         </is>
       </c>
       <c r="B182">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C182">
         <v>5</v>
@@ -5463,7 +5422,7 @@
         </is>
       </c>
       <c r="B183">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C183">
         <v>5</v>
@@ -5488,7 +5447,7 @@
         </is>
       </c>
       <c r="B184">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C184">
         <v>5</v>
@@ -5513,7 +5472,7 @@
         </is>
       </c>
       <c r="B185">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C185">
         <v>5</v>
@@ -5538,7 +5497,7 @@
         </is>
       </c>
       <c r="B186">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C186">
         <v>5</v>
@@ -5563,7 +5522,7 @@
         </is>
       </c>
       <c r="B187">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C187">
         <v>5</v>
@@ -5588,7 +5547,7 @@
         </is>
       </c>
       <c r="B188">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C188">
         <v>5</v>
@@ -5613,7 +5572,7 @@
         </is>
       </c>
       <c r="B189">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C189">
         <v>5</v>
@@ -5638,7 +5597,7 @@
         </is>
       </c>
       <c r="B190">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C190">
         <v>5</v>
@@ -5663,7 +5622,7 @@
         </is>
       </c>
       <c r="B191">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C191">
         <v>5</v>
@@ -5688,7 +5647,7 @@
         </is>
       </c>
       <c r="B192">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C192">
         <v>5</v>
@@ -5713,7 +5672,7 @@
         </is>
       </c>
       <c r="B193">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C193">
         <v>5</v>
@@ -5738,7 +5697,7 @@
         </is>
       </c>
       <c r="B194">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C194">
         <v>5</v>
@@ -5763,7 +5722,7 @@
         </is>
       </c>
       <c r="B195">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C195">
         <v>5</v>
@@ -5788,7 +5747,7 @@
         </is>
       </c>
       <c r="B196">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C196">
         <v>5</v>
@@ -5813,7 +5772,7 @@
         </is>
       </c>
       <c r="B197">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C197">
         <v>5</v>
@@ -5838,7 +5797,7 @@
         </is>
       </c>
       <c r="B198">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C198">
         <v>5</v>
@@ -5863,7 +5822,7 @@
         </is>
       </c>
       <c r="B199">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C199">
         <v>5</v>
@@ -5888,7 +5847,7 @@
         </is>
       </c>
       <c r="B200">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C200">
         <v>5</v>
@@ -5913,7 +5872,7 @@
         </is>
       </c>
       <c r="B201">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C201">
         <v>5</v>
@@ -5938,7 +5897,7 @@
         </is>
       </c>
       <c r="B202">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C202">
         <v>5</v>
@@ -5963,7 +5922,7 @@
         </is>
       </c>
       <c r="B203">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C203">
         <v>5</v>
@@ -5988,7 +5947,7 @@
         </is>
       </c>
       <c r="B204">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -6013,7 +5972,7 @@
         </is>
       </c>
       <c r="B205">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -6038,7 +5997,7 @@
         </is>
       </c>
       <c r="B206">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -6063,7 +6022,7 @@
         </is>
       </c>
       <c r="B207">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -6088,7 +6047,7 @@
         </is>
       </c>
       <c r="B208">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C208">
         <v>5</v>
@@ -6113,7 +6072,7 @@
         </is>
       </c>
       <c r="B209">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C209">
         <v>5</v>
@@ -6138,7 +6097,7 @@
         </is>
       </c>
       <c r="B210">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C210">
         <v>5</v>
@@ -6163,7 +6122,7 @@
         </is>
       </c>
       <c r="B211">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C211">
         <v>5</v>
@@ -6188,7 +6147,7 @@
         </is>
       </c>
       <c r="B212">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C212">
         <v>5</v>
@@ -6213,7 +6172,7 @@
         </is>
       </c>
       <c r="B213">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C213">
         <v>5</v>
@@ -6238,7 +6197,7 @@
         </is>
       </c>
       <c r="B214">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C214">
         <v>5</v>
@@ -6263,7 +6222,7 @@
         </is>
       </c>
       <c r="B215">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C215">
         <v>5</v>
@@ -6288,7 +6247,7 @@
         </is>
       </c>
       <c r="B216">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C216">
         <v>5</v>
@@ -6313,7 +6272,7 @@
         </is>
       </c>
       <c r="B217">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C217">
         <v>5</v>
@@ -6338,7 +6297,7 @@
         </is>
       </c>
       <c r="B218">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C218">
         <v>5</v>
@@ -6363,7 +6322,7 @@
         </is>
       </c>
       <c r="B219">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C219">
         <v>5</v>
@@ -6388,7 +6347,7 @@
         </is>
       </c>
       <c r="B220">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C220">
         <v>5</v>
@@ -6413,7 +6372,7 @@
         </is>
       </c>
       <c r="B221">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C221">
         <v>5</v>
@@ -6438,7 +6397,7 @@
         </is>
       </c>
       <c r="B222">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C222">
         <v>5</v>
@@ -6463,7 +6422,7 @@
         </is>
       </c>
       <c r="B223">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C223">
         <v>5</v>
@@ -6488,7 +6447,7 @@
         </is>
       </c>
       <c r="B224">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C224">
         <v>5</v>
@@ -6513,7 +6472,7 @@
         </is>
       </c>
       <c r="B225">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C225">
         <v>5</v>
@@ -6538,7 +6497,7 @@
         </is>
       </c>
       <c r="B226">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C226">
         <v>5</v>
@@ -6563,7 +6522,7 @@
         </is>
       </c>
       <c r="B227">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C227">
         <v>5</v>
@@ -6588,7 +6547,7 @@
         </is>
       </c>
       <c r="B228">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C228">
         <v>5</v>
@@ -6613,7 +6572,7 @@
         </is>
       </c>
       <c r="B229">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C229">
         <v>5</v>
@@ -6638,7 +6597,7 @@
         </is>
       </c>
       <c r="B230">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C230">
         <v>5</v>
@@ -6663,7 +6622,7 @@
         </is>
       </c>
       <c r="B231">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C231">
         <v>5</v>
@@ -6688,7 +6647,7 @@
         </is>
       </c>
       <c r="B232">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C232">
         <v>5</v>
@@ -6713,7 +6672,7 @@
         </is>
       </c>
       <c r="B233">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C233">
         <v>5</v>
@@ -6738,7 +6697,7 @@
         </is>
       </c>
       <c r="B234">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C234">
         <v>5</v>
@@ -6763,7 +6722,7 @@
         </is>
       </c>
       <c r="B235">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C235">
         <v>5</v>
@@ -6788,7 +6747,7 @@
         </is>
       </c>
       <c r="B236">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C236">
         <v>5</v>
@@ -6813,7 +6772,7 @@
         </is>
       </c>
       <c r="B237">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C237">
         <v>5</v>
@@ -6838,7 +6797,7 @@
         </is>
       </c>
       <c r="B238">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C238">
         <v>5</v>
@@ -6863,7 +6822,7 @@
         </is>
       </c>
       <c r="B239">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C239">
         <v>5</v>
@@ -6888,7 +6847,7 @@
         </is>
       </c>
       <c r="B240">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C240">
         <v>5</v>
@@ -6913,7 +6872,7 @@
         </is>
       </c>
       <c r="B241">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C241">
         <v>5</v>
@@ -6938,7 +6897,7 @@
         </is>
       </c>
       <c r="B242">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C242">
         <v>5</v>
@@ -6963,7 +6922,7 @@
         </is>
       </c>
       <c r="B243">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C243">
         <v>5</v>
@@ -6988,7 +6947,7 @@
         </is>
       </c>
       <c r="B244">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C244">
         <v>5</v>
@@ -7013,7 +6972,7 @@
         </is>
       </c>
       <c r="B245">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C245">
         <v>5</v>
@@ -7038,7 +6997,7 @@
         </is>
       </c>
       <c r="B246">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C246">
         <v>5</v>
@@ -7063,7 +7022,7 @@
         </is>
       </c>
       <c r="B247">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C247">
         <v>5</v>
@@ -7088,7 +7047,7 @@
         </is>
       </c>
       <c r="B248">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C248">
         <v>5</v>
@@ -7113,7 +7072,7 @@
         </is>
       </c>
       <c r="B249">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C249">
         <v>5</v>
@@ -7138,7 +7097,7 @@
         </is>
       </c>
       <c r="B250">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C250">
         <v>5</v>
@@ -7163,7 +7122,7 @@
         </is>
       </c>
       <c r="B251">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C251">
         <v>5</v>
@@ -7188,7 +7147,7 @@
         </is>
       </c>
       <c r="B252">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C252">
         <v>5</v>
@@ -7213,7 +7172,7 @@
         </is>
       </c>
       <c r="B253">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C253">
         <v>5</v>
@@ -7238,7 +7197,7 @@
         </is>
       </c>
       <c r="B254">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C254">
         <v>5</v>
@@ -7263,7 +7222,7 @@
         </is>
       </c>
       <c r="B255">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C255">
         <v>5</v>
@@ -7288,7 +7247,7 @@
         </is>
       </c>
       <c r="B256">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C256">
         <v>5</v>
@@ -7313,7 +7272,7 @@
         </is>
       </c>
       <c r="B257">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C257">
         <v>5</v>
@@ -7338,7 +7297,7 @@
         </is>
       </c>
       <c r="B258">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C258">
         <v>5</v>
@@ -7363,7 +7322,7 @@
         </is>
       </c>
       <c r="B259">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C259">
         <v>5</v>
@@ -7388,7 +7347,7 @@
         </is>
       </c>
       <c r="B260">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C260">
         <v>5</v>
@@ -7413,7 +7372,7 @@
         </is>
       </c>
       <c r="B261">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C261">
         <v>5</v>
@@ -7438,7 +7397,7 @@
         </is>
       </c>
       <c r="B262">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C262">
         <v>5</v>
@@ -7463,7 +7422,7 @@
         </is>
       </c>
       <c r="B263">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C263">
         <v>5</v>
@@ -7488,7 +7447,7 @@
         </is>
       </c>
       <c r="B264">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C264">
         <v>5</v>
@@ -7513,7 +7472,7 @@
         </is>
       </c>
       <c r="B265">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C265">
         <v>5</v>
@@ -7538,7 +7497,7 @@
         </is>
       </c>
       <c r="B266">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C266">
         <v>5</v>
@@ -7563,7 +7522,7 @@
         </is>
       </c>
       <c r="B267">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C267">
         <v>5</v>
@@ -7588,7 +7547,7 @@
         </is>
       </c>
       <c r="B268">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C268">
         <v>5</v>
@@ -7613,7 +7572,7 @@
         </is>
       </c>
       <c r="B269">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C269">
         <v>5</v>
@@ -7638,7 +7597,7 @@
         </is>
       </c>
       <c r="B270">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C270">
         <v>5</v>
@@ -7663,7 +7622,7 @@
         </is>
       </c>
       <c r="B271">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C271">
         <v>5</v>
@@ -7688,7 +7647,7 @@
         </is>
       </c>
       <c r="B272">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C272">
         <v>5</v>
@@ -7713,7 +7672,7 @@
         </is>
       </c>
       <c r="B273">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C273">
         <v>5</v>
@@ -7738,7 +7697,7 @@
         </is>
       </c>
       <c r="B274">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C274">
         <v>5</v>
@@ -7763,7 +7722,7 @@
         </is>
       </c>
       <c r="B275">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C275">
         <v>5</v>
@@ -7788,7 +7747,7 @@
         </is>
       </c>
       <c r="B276">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C276">
         <v>5</v>
@@ -7813,7 +7772,7 @@
         </is>
       </c>
       <c r="B277">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C277">
         <v>5</v>
@@ -7838,7 +7797,7 @@
         </is>
       </c>
       <c r="B278">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C278">
         <v>5</v>
@@ -7863,7 +7822,7 @@
         </is>
       </c>
       <c r="B279">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C279">
         <v>5</v>
@@ -7888,7 +7847,7 @@
         </is>
       </c>
       <c r="B280">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -7913,7 +7872,7 @@
         </is>
       </c>
       <c r="B281">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -7938,7 +7897,7 @@
         </is>
       </c>
       <c r="B282">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C282">
         <v>5</v>
@@ -7963,7 +7922,7 @@
         </is>
       </c>
       <c r="B283">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -7988,7 +7947,7 @@
         </is>
       </c>
       <c r="B284">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -8013,7 +7972,7 @@
         </is>
       </c>
       <c r="B285">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8038,7 +7997,7 @@
         </is>
       </c>
       <c r="B286">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -8063,7 +8022,7 @@
         </is>
       </c>
       <c r="B287">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C287">
         <v>5</v>
@@ -8088,7 +8047,7 @@
         </is>
       </c>
       <c r="B288">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C288">
         <v>5</v>
@@ -8113,7 +8072,7 @@
         </is>
       </c>
       <c r="B289">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C289">
         <v>5</v>
@@ -8138,7 +8097,7 @@
         </is>
       </c>
       <c r="B290">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C290">
         <v>5</v>
@@ -8163,7 +8122,7 @@
         </is>
       </c>
       <c r="B291">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C291">
         <v>5</v>
@@ -8188,7 +8147,7 @@
         </is>
       </c>
       <c r="B292">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C292">
         <v>5</v>
@@ -8213,7 +8172,7 @@
         </is>
       </c>
       <c r="B293">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C293">
         <v>5</v>
@@ -8238,7 +8197,7 @@
         </is>
       </c>
       <c r="B294">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C294">
         <v>5</v>
@@ -8263,7 +8222,7 @@
         </is>
       </c>
       <c r="B295">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C295">
         <v>5</v>
@@ -8288,7 +8247,7 @@
         </is>
       </c>
       <c r="B296">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C296">
         <v>5</v>
@@ -8313,7 +8272,7 @@
         </is>
       </c>
       <c r="B297">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C297">
         <v>5</v>
@@ -8338,7 +8297,7 @@
         </is>
       </c>
       <c r="B298">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C298">
         <v>5</v>
@@ -8363,7 +8322,7 @@
         </is>
       </c>
       <c r="B299">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C299">
         <v>5</v>
@@ -8388,7 +8347,7 @@
         </is>
       </c>
       <c r="B300">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C300">
         <v>5</v>
@@ -8413,7 +8372,7 @@
         </is>
       </c>
       <c r="B301">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C301">
         <v>5</v>
@@ -8438,7 +8397,7 @@
         </is>
       </c>
       <c r="B302">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C302">
         <v>5</v>
@@ -8463,7 +8422,7 @@
         </is>
       </c>
       <c r="B303">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C303">
         <v>5</v>
@@ -8488,7 +8447,7 @@
         </is>
       </c>
       <c r="B304">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C304">
         <v>5</v>
@@ -8513,7 +8472,7 @@
         </is>
       </c>
       <c r="B305">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C305">
         <v>5</v>
@@ -8538,7 +8497,7 @@
         </is>
       </c>
       <c r="B306">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C306">
         <v>5</v>
@@ -8563,7 +8522,7 @@
         </is>
       </c>
       <c r="B307">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C307">
         <v>5</v>
@@ -8588,7 +8547,7 @@
         </is>
       </c>
       <c r="B308">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C308">
         <v>5</v>
@@ -8613,7 +8572,7 @@
         </is>
       </c>
       <c r="B309">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C309">
         <v>5</v>
@@ -8638,7 +8597,7 @@
         </is>
       </c>
       <c r="B310">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C310">
         <v>5</v>
@@ -8663,7 +8622,7 @@
         </is>
       </c>
       <c r="B311">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C311">
         <v>5</v>
@@ -8688,7 +8647,7 @@
         </is>
       </c>
       <c r="B312">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C312">
         <v>5</v>
@@ -8713,7 +8672,7 @@
         </is>
       </c>
       <c r="B313">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C313">
         <v>5</v>
@@ -8738,7 +8697,7 @@
         </is>
       </c>
       <c r="B314">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C314">
         <v>5</v>
@@ -8763,7 +8722,7 @@
         </is>
       </c>
       <c r="B315">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C315">
         <v>5</v>
@@ -8788,7 +8747,7 @@
         </is>
       </c>
       <c r="B316">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C316">
         <v>5</v>
@@ -8813,7 +8772,7 @@
         </is>
       </c>
       <c r="B317">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C317">
         <v>5</v>
@@ -8838,7 +8797,7 @@
         </is>
       </c>
       <c r="B318">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C318">
         <v>5</v>
@@ -8863,7 +8822,7 @@
         </is>
       </c>
       <c r="B319">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C319">
         <v>5</v>
@@ -8888,7 +8847,7 @@
         </is>
       </c>
       <c r="B320">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C320">
         <v>5</v>
@@ -8913,7 +8872,7 @@
         </is>
       </c>
       <c r="B321">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C321">
         <v>5</v>
@@ -8938,7 +8897,7 @@
         </is>
       </c>
       <c r="B322">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C322">
         <v>5</v>
@@ -8963,7 +8922,7 @@
         </is>
       </c>
       <c r="B323">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C323">
         <v>5</v>
@@ -8988,7 +8947,7 @@
         </is>
       </c>
       <c r="B324">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C324">
         <v>5</v>
@@ -9013,7 +8972,7 @@
         </is>
       </c>
       <c r="B325">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C325">
         <v>5</v>
@@ -9038,7 +8997,7 @@
         </is>
       </c>
       <c r="B326">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C326">
         <v>5</v>
@@ -9063,7 +9022,7 @@
         </is>
       </c>
       <c r="B327">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C327">
         <v>5</v>
@@ -9088,7 +9047,7 @@
         </is>
       </c>
       <c r="B328">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C328">
         <v>5</v>
@@ -9113,7 +9072,7 @@
         </is>
       </c>
       <c r="B329">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C329">
         <v>5</v>
@@ -9138,7 +9097,7 @@
         </is>
       </c>
       <c r="B330">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C330">
         <v>5</v>
@@ -9163,7 +9122,7 @@
         </is>
       </c>
       <c r="B331">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C331">
         <v>5</v>
@@ -9188,7 +9147,7 @@
         </is>
       </c>
       <c r="B332">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C332">
         <v>5</v>
@@ -9213,7 +9172,7 @@
         </is>
       </c>
       <c r="B333">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C333">
         <v>5</v>
@@ -9238,7 +9197,7 @@
         </is>
       </c>
       <c r="B334">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C334">
         <v>5</v>
@@ -9263,7 +9222,7 @@
         </is>
       </c>
       <c r="B335">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C335">
         <v>5</v>
@@ -9288,7 +9247,7 @@
         </is>
       </c>
       <c r="B336">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C336">
         <v>5</v>
@@ -9313,7 +9272,7 @@
         </is>
       </c>
       <c r="B337">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C337">
         <v>5</v>
@@ -9338,7 +9297,7 @@
         </is>
       </c>
       <c r="B338">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C338">
         <v>5</v>
@@ -9363,7 +9322,7 @@
         </is>
       </c>
       <c r="B339">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C339">
         <v>5</v>
@@ -9388,7 +9347,7 @@
         </is>
       </c>
       <c r="B340">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C340">
         <v>5</v>
@@ -9413,7 +9372,7 @@
         </is>
       </c>
       <c r="B341">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C341">
         <v>5</v>
@@ -9438,7 +9397,7 @@
         </is>
       </c>
       <c r="B342">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C342">
         <v>5</v>
@@ -9463,7 +9422,7 @@
         </is>
       </c>
       <c r="B343">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C343">
         <v>5</v>
@@ -9488,7 +9447,7 @@
         </is>
       </c>
       <c r="B344">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C344">
         <v>5</v>
@@ -9513,7 +9472,7 @@
         </is>
       </c>
       <c r="B345">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C345">
         <v>5</v>
@@ -9538,7 +9497,7 @@
         </is>
       </c>
       <c r="B346">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C346">
         <v>5</v>
@@ -9563,7 +9522,7 @@
         </is>
       </c>
       <c r="B347">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C347">
         <v>5</v>
@@ -9588,7 +9547,7 @@
         </is>
       </c>
       <c r="B348">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C348">
         <v>5</v>
@@ -9613,7 +9572,7 @@
         </is>
       </c>
       <c r="B349">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C349">
         <v>5</v>
@@ -9638,7 +9597,7 @@
         </is>
       </c>
       <c r="B350">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C350">
         <v>5</v>
@@ -9663,7 +9622,7 @@
         </is>
       </c>
       <c r="B351">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C351">
         <v>5</v>
@@ -9688,7 +9647,7 @@
         </is>
       </c>
       <c r="B352">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C352">
         <v>5</v>
@@ -9713,7 +9672,7 @@
         </is>
       </c>
       <c r="B353">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C353">
         <v>5</v>
@@ -9738,7 +9697,7 @@
         </is>
       </c>
       <c r="B354">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C354">
         <v>5</v>
@@ -9763,7 +9722,7 @@
         </is>
       </c>
       <c r="B355">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C355">
         <v>5</v>
@@ -9788,7 +9747,7 @@
         </is>
       </c>
       <c r="B356">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C356">
         <v>5</v>
@@ -9813,7 +9772,7 @@
         </is>
       </c>
       <c r="B357">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C357">
         <v>5</v>
@@ -9838,7 +9797,7 @@
         </is>
       </c>
       <c r="B358">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C358">
         <v>5</v>
@@ -9863,7 +9822,7 @@
         </is>
       </c>
       <c r="B359">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C359">
         <v>5</v>
@@ -9888,7 +9847,7 @@
         </is>
       </c>
       <c r="B360">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C360">
         <v>5</v>
@@ -9913,7 +9872,7 @@
         </is>
       </c>
       <c r="B361">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C361">
         <v>5</v>
@@ -9938,7 +9897,7 @@
         </is>
       </c>
       <c r="B362">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C362">
         <v>5</v>
@@ -9963,7 +9922,7 @@
         </is>
       </c>
       <c r="B363">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C363">
         <v>5</v>
@@ -9988,7 +9947,7 @@
         </is>
       </c>
       <c r="B364">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C364">
         <v>5</v>
@@ -10013,7 +9972,7 @@
         </is>
       </c>
       <c r="B365">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C365">
         <v>5</v>
@@ -10038,7 +9997,7 @@
         </is>
       </c>
       <c r="B366">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C366">
         <v>5</v>
@@ -10063,7 +10022,7 @@
         </is>
       </c>
       <c r="B367">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C367">
         <v>5</v>
@@ -10088,7 +10047,7 @@
         </is>
       </c>
       <c r="B368">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C368">
         <v>5</v>
@@ -10113,7 +10072,7 @@
         </is>
       </c>
       <c r="B369">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C369">
         <v>5</v>
@@ -10138,7 +10097,7 @@
         </is>
       </c>
       <c r="B370">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C370">
         <v>5</v>
@@ -10163,7 +10122,7 @@
         </is>
       </c>
       <c r="B371">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C371">
         <v>5</v>
@@ -10188,7 +10147,7 @@
         </is>
       </c>
       <c r="B372">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C372">
         <v>5</v>
@@ -10213,7 +10172,7 @@
         </is>
       </c>
       <c r="B373">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C373">
         <v>5</v>
@@ -10238,7 +10197,7 @@
         </is>
       </c>
       <c r="B374">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C374">
         <v>5</v>
@@ -10263,7 +10222,7 @@
         </is>
       </c>
       <c r="B375">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C375">
         <v>5</v>
@@ -10288,7 +10247,7 @@
         </is>
       </c>
       <c r="B376">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C376">
         <v>5</v>
@@ -10313,7 +10272,7 @@
         </is>
       </c>
       <c r="B377">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C377">
         <v>5</v>
@@ -10338,7 +10297,7 @@
         </is>
       </c>
       <c r="B378">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C378">
         <v>5</v>
@@ -10363,7 +10322,7 @@
         </is>
       </c>
       <c r="B379">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C379">
         <v>5</v>
@@ -10388,7 +10347,7 @@
         </is>
       </c>
       <c r="B380">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C380">
         <v>5</v>
@@ -10413,7 +10372,7 @@
         </is>
       </c>
       <c r="B381">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C381">
         <v>5</v>
@@ -10438,7 +10397,7 @@
         </is>
       </c>
       <c r="B382">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C382">
         <v>5</v>
@@ -10463,7 +10422,7 @@
         </is>
       </c>
       <c r="B383">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C383">
         <v>5</v>
@@ -10488,7 +10447,7 @@
         </is>
       </c>
       <c r="B384">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C384">
         <v>5</v>
@@ -10513,7 +10472,7 @@
         </is>
       </c>
       <c r="B385">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C385">
         <v>5</v>
@@ -10538,7 +10497,7 @@
         </is>
       </c>
       <c r="B386">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C386">
         <v>5</v>
@@ -10563,7 +10522,7 @@
         </is>
       </c>
       <c r="B387">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C387">
         <v>5</v>
@@ -10588,7 +10547,7 @@
         </is>
       </c>
       <c r="B388">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C388">
         <v>5</v>
@@ -10613,7 +10572,7 @@
         </is>
       </c>
       <c r="B389">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C389">
         <v>5</v>
@@ -10638,7 +10597,7 @@
         </is>
       </c>
       <c r="B390">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C390">
         <v>5</v>
@@ -10663,7 +10622,7 @@
         </is>
       </c>
       <c r="B391">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C391">
         <v>5</v>
@@ -10688,7 +10647,7 @@
         </is>
       </c>
       <c r="B392">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C392">
         <v>5</v>
@@ -10713,7 +10672,7 @@
         </is>
       </c>
       <c r="B393">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C393">
         <v>5</v>
@@ -10738,7 +10697,7 @@
         </is>
       </c>
       <c r="B394">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C394">
         <v>5</v>
@@ -10763,7 +10722,7 @@
         </is>
       </c>
       <c r="B395">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C395">
         <v>5</v>
@@ -10788,7 +10747,7 @@
         </is>
       </c>
       <c r="B396">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C396">
         <v>5</v>
@@ -10813,7 +10772,7 @@
         </is>
       </c>
       <c r="B397">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C397">
         <v>5</v>
@@ -10838,7 +10797,7 @@
         </is>
       </c>
       <c r="B398">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C398">
         <v>5</v>
@@ -10863,7 +10822,7 @@
         </is>
       </c>
       <c r="B399">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C399">
         <v>5</v>
@@ -10888,7 +10847,7 @@
         </is>
       </c>
       <c r="B400">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C400">
         <v>5</v>
@@ -10913,7 +10872,7 @@
         </is>
       </c>
       <c r="B401">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C401">
         <v>5</v>
@@ -10938,7 +10897,7 @@
         </is>
       </c>
       <c r="B402">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C402">
         <v>5</v>
@@ -10963,7 +10922,7 @@
         </is>
       </c>
       <c r="B403">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C403">
         <v>5</v>
@@ -10988,7 +10947,7 @@
         </is>
       </c>
       <c r="B404">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C404">
         <v>5</v>
@@ -11013,7 +10972,7 @@
         </is>
       </c>
       <c r="B405">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C405">
         <v>5</v>
@@ -11038,7 +10997,7 @@
         </is>
       </c>
       <c r="B406">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C406">
         <v>5</v>
@@ -11063,7 +11022,7 @@
         </is>
       </c>
       <c r="B407">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C407">
         <v>5</v>
@@ -11088,7 +11047,7 @@
         </is>
       </c>
       <c r="B408">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C408">
         <v>5</v>
@@ -11113,7 +11072,7 @@
         </is>
       </c>
       <c r="B409">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C409">
         <v>5</v>
@@ -11138,7 +11097,7 @@
         </is>
       </c>
       <c r="B410">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C410">
         <v>5</v>
@@ -11163,7 +11122,7 @@
         </is>
       </c>
       <c r="B411">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C411">
         <v>5</v>
@@ -11188,7 +11147,7 @@
         </is>
       </c>
       <c r="B412">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C412">
         <v>5</v>
@@ -11213,7 +11172,7 @@
         </is>
       </c>
       <c r="B413">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C413">
         <v>5</v>
@@ -11238,7 +11197,7 @@
         </is>
       </c>
       <c r="B414">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C414">
         <v>5</v>
@@ -11263,7 +11222,7 @@
         </is>
       </c>
       <c r="B415">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C415">
         <v>5</v>
@@ -11288,7 +11247,7 @@
         </is>
       </c>
       <c r="B416">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C416">
         <v>5</v>
@@ -11313,7 +11272,7 @@
         </is>
       </c>
       <c r="B417">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C417">
         <v>5</v>
@@ -11338,7 +11297,7 @@
         </is>
       </c>
       <c r="B418">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C418">
         <v>5</v>
@@ -11363,7 +11322,7 @@
         </is>
       </c>
       <c r="B419">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C419">
         <v>5</v>
@@ -11388,7 +11347,7 @@
         </is>
       </c>
       <c r="B420">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C420">
         <v>5</v>
@@ -11413,7 +11372,7 @@
         </is>
       </c>
       <c r="B421">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C421">
         <v>5</v>
@@ -11438,7 +11397,7 @@
         </is>
       </c>
       <c r="B422">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C422">
         <v>5</v>
@@ -11463,7 +11422,7 @@
         </is>
       </c>
       <c r="B423">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C423">
         <v>5</v>
@@ -11488,7 +11447,7 @@
         </is>
       </c>
       <c r="B424">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C424">
         <v>5</v>
@@ -11513,7 +11472,7 @@
         </is>
       </c>
       <c r="B425">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C425">
         <v>5</v>
@@ -11538,7 +11497,7 @@
         </is>
       </c>
       <c r="B426">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C426">
         <v>5</v>
@@ -11563,7 +11522,7 @@
         </is>
       </c>
       <c r="B427">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C427">
         <v>5</v>
@@ -11588,7 +11547,7 @@
         </is>
       </c>
       <c r="B428">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C428">
         <v>5</v>
@@ -11613,7 +11572,7 @@
         </is>
       </c>
       <c r="B429">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C429">
         <v>5</v>
@@ -11638,7 +11597,7 @@
         </is>
       </c>
       <c r="B430">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C430">
         <v>5</v>
@@ -11663,7 +11622,7 @@
         </is>
       </c>
       <c r="B431">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C431">
         <v>5</v>
@@ -11688,7 +11647,7 @@
         </is>
       </c>
       <c r="B432">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C432">
         <v>5</v>
@@ -11713,7 +11672,7 @@
         </is>
       </c>
       <c r="B433">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C433">
         <v>5</v>
@@ -11738,7 +11697,7 @@
         </is>
       </c>
       <c r="B434">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C434">
         <v>5</v>
@@ -11763,7 +11722,7 @@
         </is>
       </c>
       <c r="B435">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C435">
         <v>5</v>
@@ -11788,7 +11747,7 @@
         </is>
       </c>
       <c r="B436">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C436">
         <v>5</v>
@@ -11813,7 +11772,7 @@
         </is>
       </c>
       <c r="B437">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C437">
         <v>5</v>
@@ -11838,7 +11797,7 @@
         </is>
       </c>
       <c r="B438">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C438">
         <v>5</v>
@@ -11863,7 +11822,7 @@
         </is>
       </c>
       <c r="B439">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C439">
         <v>5</v>
@@ -11888,7 +11847,7 @@
         </is>
       </c>
       <c r="B440">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C440">
         <v>5</v>
@@ -11913,7 +11872,7 @@
         </is>
       </c>
       <c r="B441">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C441">
         <v>5</v>
@@ -11938,7 +11897,7 @@
         </is>
       </c>
       <c r="B442">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C442">
         <v>5</v>
@@ -11963,7 +11922,7 @@
         </is>
       </c>
       <c r="B443">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C443">
         <v>5</v>
@@ -11988,7 +11947,7 @@
         </is>
       </c>
       <c r="B444">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C444">
         <v>5</v>
@@ -12013,7 +11972,7 @@
         </is>
       </c>
       <c r="B445">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C445">
         <v>5</v>
@@ -12038,7 +11997,7 @@
         </is>
       </c>
       <c r="B446">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C446">
         <v>5</v>
@@ -12063,7 +12022,7 @@
         </is>
       </c>
       <c r="B447">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C447">
         <v>5</v>
@@ -12088,7 +12047,7 @@
         </is>
       </c>
       <c r="B448">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C448">
         <v>5</v>
@@ -12113,7 +12072,7 @@
         </is>
       </c>
       <c r="B449">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C449">
         <v>5</v>
@@ -12138,7 +12097,7 @@
         </is>
       </c>
       <c r="B450">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C450">
         <v>5</v>
@@ -12163,7 +12122,7 @@
         </is>
       </c>
       <c r="B451">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C451">
         <v>5</v>
@@ -12188,7 +12147,7 @@
         </is>
       </c>
       <c r="B452">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C452">
         <v>5</v>
@@ -12213,7 +12172,7 @@
         </is>
       </c>
       <c r="B453">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C453">
         <v>5</v>
@@ -12238,7 +12197,7 @@
         </is>
       </c>
       <c r="B454">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C454">
         <v>5</v>
@@ -12263,7 +12222,7 @@
         </is>
       </c>
       <c r="B455">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C455">
         <v>5</v>
@@ -12288,7 +12247,7 @@
         </is>
       </c>
       <c r="B456">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C456">
         <v>5</v>
@@ -12313,7 +12272,7 @@
         </is>
       </c>
       <c r="B457">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C457">
         <v>5</v>
@@ -12338,7 +12297,7 @@
         </is>
       </c>
       <c r="B458">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C458">
         <v>5</v>
@@ -12363,7 +12322,7 @@
         </is>
       </c>
       <c r="B459">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C459">
         <v>5</v>
@@ -12388,7 +12347,7 @@
         </is>
       </c>
       <c r="B460">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C460">
         <v>5</v>
@@ -12413,7 +12372,7 @@
         </is>
       </c>
       <c r="B461">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C461">
         <v>5</v>
@@ -12438,7 +12397,7 @@
         </is>
       </c>
       <c r="B462">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C462">
         <v>5</v>
@@ -12463,7 +12422,7 @@
         </is>
       </c>
       <c r="B463">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C463">
         <v>5</v>
@@ -12488,7 +12447,7 @@
         </is>
       </c>
       <c r="B464">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C464">
         <v>5</v>
@@ -12513,7 +12472,7 @@
         </is>
       </c>
       <c r="B465">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C465">
         <v>5</v>
@@ -12538,7 +12497,7 @@
         </is>
       </c>
       <c r="B466">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C466">
         <v>5</v>
@@ -12563,7 +12522,7 @@
         </is>
       </c>
       <c r="B467">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C467">
         <v>5</v>
@@ -12588,7 +12547,7 @@
         </is>
       </c>
       <c r="B468">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C468">
         <v>5</v>
@@ -12613,7 +12572,7 @@
         </is>
       </c>
       <c r="B469">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C469">
         <v>5</v>
@@ -12638,7 +12597,7 @@
         </is>
       </c>
       <c r="B470">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C470">
         <v>5</v>
@@ -12663,7 +12622,7 @@
         </is>
       </c>
       <c r="B471">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C471">
         <v>5</v>
@@ -12688,7 +12647,7 @@
         </is>
       </c>
       <c r="B472">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C472">
         <v>5</v>
@@ -12713,7 +12672,7 @@
         </is>
       </c>
       <c r="B473">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C473">
         <v>5</v>
@@ -12738,7 +12697,7 @@
         </is>
       </c>
       <c r="B474">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C474">
         <v>5</v>
@@ -12763,7 +12722,7 @@
         </is>
       </c>
       <c r="B475">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C475">
         <v>5</v>
@@ -12788,7 +12747,7 @@
         </is>
       </c>
       <c r="B476">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C476">
         <v>5</v>
@@ -12813,7 +12772,7 @@
         </is>
       </c>
       <c r="B477">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C477">
         <v>5</v>
@@ -12838,7 +12797,7 @@
         </is>
       </c>
       <c r="B478">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C478">
         <v>5</v>
@@ -12863,7 +12822,7 @@
         </is>
       </c>
       <c r="B479">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C479">
         <v>5</v>
@@ -12888,7 +12847,7 @@
         </is>
       </c>
       <c r="B480">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C480">
         <v>5</v>
@@ -12913,7 +12872,7 @@
         </is>
       </c>
       <c r="B481">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C481">
         <v>5</v>
@@ -12938,7 +12897,7 @@
         </is>
       </c>
       <c r="B482">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C482">
         <v>5</v>
@@ -12963,7 +12922,7 @@
         </is>
       </c>
       <c r="B483">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C483">
         <v>5</v>
@@ -12988,7 +12947,7 @@
         </is>
       </c>
       <c r="B484">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C484">
         <v>5</v>
@@ -13013,7 +12972,7 @@
         </is>
       </c>
       <c r="B485">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C485">
         <v>5</v>
@@ -13038,7 +12997,7 @@
         </is>
       </c>
       <c r="B486">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C486">
         <v>5</v>
@@ -13063,7 +13022,7 @@
         </is>
       </c>
       <c r="B487">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C487">
         <v>5</v>
@@ -13088,7 +13047,7 @@
         </is>
       </c>
       <c r="B488">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C488">
         <v>5</v>
@@ -13113,7 +13072,7 @@
         </is>
       </c>
       <c r="B489">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C489">
         <v>5</v>
@@ -13138,7 +13097,7 @@
         </is>
       </c>
       <c r="B490">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C490">
         <v>5</v>
@@ -13163,7 +13122,7 @@
         </is>
       </c>
       <c r="B491">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C491">
         <v>5</v>
@@ -13188,7 +13147,7 @@
         </is>
       </c>
       <c r="B492">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C492">
         <v>5</v>
@@ -13213,7 +13172,7 @@
         </is>
       </c>
       <c r="B493">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C493">
         <v>5</v>
@@ -13238,7 +13197,7 @@
         </is>
       </c>
       <c r="B494">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C494">
         <v>5</v>
@@ -13263,7 +13222,7 @@
         </is>
       </c>
       <c r="B495">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C495">
         <v>5</v>
@@ -13288,7 +13247,7 @@
         </is>
       </c>
       <c r="B496">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C496">
         <v>5</v>
@@ -13313,7 +13272,7 @@
         </is>
       </c>
       <c r="B497">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C497">
         <v>5</v>
@@ -13338,7 +13297,7 @@
         </is>
       </c>
       <c r="B498">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C498">
         <v>5</v>
@@ -13363,7 +13322,7 @@
         </is>
       </c>
       <c r="B499">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C499">
         <v>5</v>
@@ -13388,7 +13347,7 @@
         </is>
       </c>
       <c r="B500">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C500">
         <v>5</v>
@@ -13413,7 +13372,7 @@
         </is>
       </c>
       <c r="B501">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C501">
         <v>5</v>
@@ -13438,7 +13397,7 @@
         </is>
       </c>
       <c r="B502">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C502">
         <v>5</v>
@@ -13463,7 +13422,7 @@
         </is>
       </c>
       <c r="B503">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C503">
         <v>5</v>
@@ -13488,7 +13447,7 @@
         </is>
       </c>
       <c r="B504">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C504">
         <v>5</v>
@@ -13513,7 +13472,7 @@
         </is>
       </c>
       <c r="B505">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C505">
         <v>5</v>
@@ -13538,7 +13497,7 @@
         </is>
       </c>
       <c r="B506">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C506">
         <v>5</v>
@@ -13563,7 +13522,7 @@
         </is>
       </c>
       <c r="B507">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C507">
         <v>5</v>
@@ -13588,7 +13547,7 @@
         </is>
       </c>
       <c r="B508">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C508">
         <v>5</v>
@@ -13613,7 +13572,7 @@
         </is>
       </c>
       <c r="B509">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C509">
         <v>5</v>
@@ -13638,7 +13597,7 @@
         </is>
       </c>
       <c r="B510">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C510">
         <v>5</v>
@@ -13663,7 +13622,7 @@
         </is>
       </c>
       <c r="B511">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C511">
         <v>5</v>
@@ -13688,7 +13647,7 @@
         </is>
       </c>
       <c r="B512">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C512">
         <v>5</v>
@@ -13713,7 +13672,7 @@
         </is>
       </c>
       <c r="B513">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C513">
         <v>5</v>
@@ -13738,7 +13697,7 @@
         </is>
       </c>
       <c r="B514">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C514">
         <v>5</v>
@@ -13763,7 +13722,7 @@
         </is>
       </c>
       <c r="B515">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C515">
         <v>5</v>
@@ -13788,7 +13747,7 @@
         </is>
       </c>
       <c r="B516">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C516">
         <v>5</v>
@@ -13813,7 +13772,7 @@
         </is>
       </c>
       <c r="B517">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C517">
         <v>5</v>
@@ -13838,7 +13797,7 @@
         </is>
       </c>
       <c r="B518">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C518">
         <v>5</v>
@@ -13863,7 +13822,7 @@
         </is>
       </c>
       <c r="B519">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C519">
         <v>5</v>
@@ -13888,7 +13847,7 @@
         </is>
       </c>
       <c r="B520">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C520">
         <v>5</v>
@@ -13913,7 +13872,7 @@
         </is>
       </c>
       <c r="B521">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C521">
         <v>5</v>
@@ -13938,7 +13897,7 @@
         </is>
       </c>
       <c r="B522">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C522">
         <v>5</v>
@@ -13963,7 +13922,7 @@
         </is>
       </c>
       <c r="B523">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C523">
         <v>5</v>
@@ -13988,7 +13947,7 @@
         </is>
       </c>
       <c r="B524">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C524">
         <v>5</v>
@@ -14013,7 +13972,7 @@
         </is>
       </c>
       <c r="B525">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C525">
         <v>5</v>
@@ -14038,7 +13997,7 @@
         </is>
       </c>
       <c r="B526">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C526">
         <v>5</v>
@@ -14063,7 +14022,7 @@
         </is>
       </c>
       <c r="B527">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C527">
         <v>5</v>
@@ -14088,7 +14047,7 @@
         </is>
       </c>
       <c r="B528">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C528">
         <v>5</v>
@@ -14113,7 +14072,7 @@
         </is>
       </c>
       <c r="B529">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C529">
         <v>5</v>
@@ -14138,7 +14097,7 @@
         </is>
       </c>
       <c r="B530">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C530">
         <v>5</v>
@@ -14163,7 +14122,7 @@
         </is>
       </c>
       <c r="B531">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C531">
         <v>5</v>
@@ -14188,7 +14147,7 @@
         </is>
       </c>
       <c r="B532">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C532">
         <v>5</v>
@@ -14213,7 +14172,7 @@
         </is>
       </c>
       <c r="B533">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C533">
         <v>5</v>
@@ -14238,7 +14197,7 @@
         </is>
       </c>
       <c r="B534">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C534">
         <v>5</v>
@@ -14263,7 +14222,7 @@
         </is>
       </c>
       <c r="B535">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C535">
         <v>5</v>
@@ -14288,7 +14247,7 @@
         </is>
       </c>
       <c r="B536">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C536">
         <v>5</v>
@@ -14313,7 +14272,7 @@
         </is>
       </c>
       <c r="B537">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C537">
         <v>5</v>
@@ -14338,7 +14297,7 @@
         </is>
       </c>
       <c r="B538">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C538">
         <v>5</v>
@@ -14363,7 +14322,7 @@
         </is>
       </c>
       <c r="B539">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C539">
         <v>5</v>
@@ -14388,7 +14347,7 @@
         </is>
       </c>
       <c r="B540">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C540">
         <v>5</v>
@@ -14413,7 +14372,7 @@
         </is>
       </c>
       <c r="B541">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C541">
         <v>5</v>
@@ -14438,7 +14397,7 @@
         </is>
       </c>
       <c r="B542">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C542">
         <v>5</v>
@@ -14463,7 +14422,7 @@
         </is>
       </c>
       <c r="B543">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C543">
         <v>5</v>
@@ -14488,7 +14447,7 @@
         </is>
       </c>
       <c r="B544">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C544">
         <v>5</v>
@@ -14513,7 +14472,7 @@
         </is>
       </c>
       <c r="B545">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C545">
         <v>5</v>
@@ -14538,7 +14497,7 @@
         </is>
       </c>
       <c r="B546">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C546">
         <v>5</v>
@@ -14563,7 +14522,7 @@
         </is>
       </c>
       <c r="B547">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C547">
         <v>5</v>
@@ -14588,7 +14547,7 @@
         </is>
       </c>
       <c r="B548">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C548">
         <v>5</v>
@@ -14613,7 +14572,7 @@
         </is>
       </c>
       <c r="B549">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C549">
         <v>5</v>
@@ -14638,7 +14597,7 @@
         </is>
       </c>
       <c r="B550">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C550">
         <v>5</v>
@@ -14663,7 +14622,7 @@
         </is>
       </c>
       <c r="B551">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C551">
         <v>5</v>
@@ -14688,7 +14647,7 @@
         </is>
       </c>
       <c r="B552">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C552">
         <v>5</v>
@@ -14713,7 +14672,7 @@
         </is>
       </c>
       <c r="B553">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C553">
         <v>5</v>
@@ -14738,7 +14697,7 @@
         </is>
       </c>
       <c r="B554">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C554">
         <v>5</v>
@@ -14763,7 +14722,7 @@
         </is>
       </c>
       <c r="B555">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C555">
         <v>5</v>
@@ -14788,7 +14747,7 @@
         </is>
       </c>
       <c r="B556">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C556">
         <v>5</v>
@@ -14813,7 +14772,7 @@
         </is>
       </c>
       <c r="B557">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C557">
         <v>5</v>
@@ -14838,7 +14797,7 @@
         </is>
       </c>
       <c r="B558">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C558">
         <v>5</v>
@@ -14863,7 +14822,7 @@
         </is>
       </c>
       <c r="B559">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C559">
         <v>5</v>
@@ -14888,7 +14847,7 @@
         </is>
       </c>
       <c r="B560">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C560">
         <v>5</v>
@@ -14913,7 +14872,7 @@
         </is>
       </c>
       <c r="B561">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C561">
         <v>5</v>
@@ -14938,7 +14897,7 @@
         </is>
       </c>
       <c r="B562">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C562">
         <v>5</v>
@@ -14963,7 +14922,7 @@
         </is>
       </c>
       <c r="B563">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C563">
         <v>5</v>
@@ -14988,7 +14947,7 @@
         </is>
       </c>
       <c r="B564">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C564">
         <v>5</v>
@@ -15013,7 +14972,7 @@
         </is>
       </c>
       <c r="B565">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C565">
         <v>5</v>
@@ -15038,7 +14997,7 @@
         </is>
       </c>
       <c r="B566">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C566">
         <v>5</v>
@@ -15063,7 +15022,7 @@
         </is>
       </c>
       <c r="B567">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C567">
         <v>5</v>
@@ -15088,7 +15047,7 @@
         </is>
       </c>
       <c r="B568">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C568">
         <v>5</v>
@@ -15113,7 +15072,7 @@
         </is>
       </c>
       <c r="B569">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C569">
         <v>5</v>
@@ -15138,7 +15097,7 @@
         </is>
       </c>
       <c r="B570">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C570">
         <v>5</v>
@@ -15163,7 +15122,7 @@
         </is>
       </c>
       <c r="B571">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C571">
         <v>5</v>
@@ -15188,7 +15147,7 @@
         </is>
       </c>
       <c r="B572">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C572">
         <v>5</v>
@@ -15213,7 +15172,7 @@
         </is>
       </c>
       <c r="B573">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C573">
         <v>5</v>
@@ -15238,7 +15197,7 @@
         </is>
       </c>
       <c r="B574">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C574">
         <v>5</v>
@@ -15263,7 +15222,7 @@
         </is>
       </c>
       <c r="B575">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C575">
         <v>5</v>
@@ -15288,7 +15247,7 @@
         </is>
       </c>
       <c r="B576">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C576">
         <v>5</v>
@@ -15313,7 +15272,7 @@
         </is>
       </c>
       <c r="B577">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C577">
         <v>5</v>
@@ -15338,7 +15297,7 @@
         </is>
       </c>
       <c r="B578">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C578">
         <v>5</v>
@@ -15363,7 +15322,7 @@
         </is>
       </c>
       <c r="B579">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C579">
         <v>5</v>
@@ -15388,7 +15347,7 @@
         </is>
       </c>
       <c r="B580">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C580">
         <v>5</v>
@@ -15413,7 +15372,7 @@
         </is>
       </c>
       <c r="B581">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C581">
         <v>5</v>
@@ -15438,7 +15397,7 @@
         </is>
       </c>
       <c r="B582">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C582">
         <v>5</v>
@@ -15463,7 +15422,7 @@
         </is>
       </c>
       <c r="B583">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C583">
         <v>5</v>
@@ -15488,7 +15447,7 @@
         </is>
       </c>
       <c r="B584">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C584">
         <v>5</v>
@@ -15513,7 +15472,7 @@
         </is>
       </c>
       <c r="B585">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C585">
         <v>5</v>
@@ -15538,7 +15497,7 @@
         </is>
       </c>
       <c r="B586">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C586">
         <v>5</v>
@@ -15563,7 +15522,7 @@
         </is>
       </c>
       <c r="B587">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C587">
         <v>5</v>
@@ -15588,7 +15547,7 @@
         </is>
       </c>
       <c r="B588">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C588">
         <v>5</v>
@@ -15613,7 +15572,7 @@
         </is>
       </c>
       <c r="B589">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C589">
         <v>5</v>
@@ -15638,7 +15597,7 @@
         </is>
       </c>
       <c r="B590">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C590">
         <v>5</v>
@@ -15663,7 +15622,7 @@
         </is>
       </c>
       <c r="B591">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C591">
         <v>5</v>
@@ -15688,7 +15647,7 @@
         </is>
       </c>
       <c r="B592">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C592">
         <v>5</v>
@@ -15713,7 +15672,7 @@
         </is>
       </c>
       <c r="B593">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C593">
         <v>5</v>
@@ -15738,7 +15697,7 @@
         </is>
       </c>
       <c r="B594">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C594">
         <v>5</v>
@@ -15763,7 +15722,7 @@
         </is>
       </c>
       <c r="B595">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C595">
         <v>5</v>
@@ -15788,7 +15747,7 @@
         </is>
       </c>
       <c r="B596">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C596">
         <v>5</v>
@@ -15813,7 +15772,7 @@
         </is>
       </c>
       <c r="B597">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C597">
         <v>5</v>
@@ -15838,7 +15797,7 @@
         </is>
       </c>
       <c r="B598">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C598">
         <v>5</v>
@@ -15863,7 +15822,7 @@
         </is>
       </c>
       <c r="B599">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C599">
         <v>5</v>
@@ -15888,7 +15847,7 @@
         </is>
       </c>
       <c r="B600">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C600">
         <v>5</v>
@@ -15913,7 +15872,7 @@
         </is>
       </c>
       <c r="B601">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C601">
         <v>5</v>
@@ -15938,7 +15897,7 @@
         </is>
       </c>
       <c r="B602">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C602">
         <v>5</v>
@@ -15963,7 +15922,7 @@
         </is>
       </c>
       <c r="B603">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C603">
         <v>5</v>
@@ -15988,7 +15947,7 @@
         </is>
       </c>
       <c r="B604">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C604">
         <v>5</v>
@@ -16013,7 +15972,7 @@
         </is>
       </c>
       <c r="B605">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C605">
         <v>5</v>
@@ -16038,7 +15997,7 @@
         </is>
       </c>
       <c r="B606">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C606">
         <v>5</v>
@@ -16063,7 +16022,7 @@
         </is>
       </c>
       <c r="B607">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C607">
         <v>5</v>
@@ -16088,7 +16047,7 @@
         </is>
       </c>
       <c r="B608">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C608">
         <v>5</v>
@@ -16113,7 +16072,7 @@
         </is>
       </c>
       <c r="B609">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C609">
         <v>5</v>
@@ -16138,7 +16097,7 @@
         </is>
       </c>
       <c r="B610">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C610">
         <v>5</v>
@@ -16163,7 +16122,7 @@
         </is>
       </c>
       <c r="B611">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C611">
         <v>5</v>
@@ -16188,7 +16147,7 @@
         </is>
       </c>
       <c r="B612">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C612">
         <v>5</v>
@@ -16213,7 +16172,7 @@
         </is>
       </c>
       <c r="B613">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C613">
         <v>5</v>
@@ -16238,7 +16197,7 @@
         </is>
       </c>
       <c r="B614">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C614">
         <v>5</v>
@@ -16263,7 +16222,7 @@
         </is>
       </c>
       <c r="B615">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C615">
         <v>5</v>
@@ -16288,7 +16247,7 @@
         </is>
       </c>
       <c r="B616">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C616">
         <v>5</v>
@@ -16313,7 +16272,7 @@
         </is>
       </c>
       <c r="B617">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C617">
         <v>5</v>
@@ -16338,7 +16297,7 @@
         </is>
       </c>
       <c r="B618">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C618">
         <v>5</v>
@@ -16363,7 +16322,7 @@
         </is>
       </c>
       <c r="B619">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C619">
         <v>5</v>
@@ -16388,7 +16347,7 @@
         </is>
       </c>
       <c r="B620">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C620">
         <v>5</v>
@@ -16413,7 +16372,7 @@
         </is>
       </c>
       <c r="B621">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C621">
         <v>5</v>
@@ -16438,7 +16397,7 @@
         </is>
       </c>
       <c r="B622">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C622">
         <v>5</v>
@@ -16463,7 +16422,7 @@
         </is>
       </c>
       <c r="B623">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C623">
         <v>5</v>
@@ -16488,7 +16447,7 @@
         </is>
       </c>
       <c r="B624">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C624">
         <v>5</v>
@@ -16513,7 +16472,7 @@
         </is>
       </c>
       <c r="B625">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C625">
         <v>5</v>
@@ -16538,7 +16497,7 @@
         </is>
       </c>
       <c r="B626">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C626">
         <v>5</v>
@@ -16563,7 +16522,7 @@
         </is>
       </c>
       <c r="B627">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C627">
         <v>5</v>
@@ -16588,7 +16547,7 @@
         </is>
       </c>
       <c r="B628">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C628">
         <v>5</v>
@@ -16613,7 +16572,7 @@
         </is>
       </c>
       <c r="B629">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C629">
         <v>5</v>
@@ -16638,7 +16597,7 @@
         </is>
       </c>
       <c r="B630">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C630">
         <v>5</v>
@@ -16663,7 +16622,7 @@
         </is>
       </c>
       <c r="B631">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C631">
         <v>5</v>
@@ -16688,7 +16647,7 @@
         </is>
       </c>
       <c r="B632">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C632">
         <v>5</v>
@@ -16713,7 +16672,7 @@
         </is>
       </c>
       <c r="B633">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C633">
         <v>5</v>
@@ -16738,7 +16697,7 @@
         </is>
       </c>
       <c r="B634">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C634">
         <v>5</v>
@@ -16763,7 +16722,7 @@
         </is>
       </c>
       <c r="B635">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C635">
         <v>5</v>
@@ -16788,7 +16747,7 @@
         </is>
       </c>
       <c r="B636">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C636">
         <v>5</v>
@@ -16813,7 +16772,7 @@
         </is>
       </c>
       <c r="B637">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C637">
         <v>5</v>
@@ -16838,7 +16797,7 @@
         </is>
       </c>
       <c r="B638">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C638">
         <v>5</v>
@@ -16863,7 +16822,7 @@
         </is>
       </c>
       <c r="B639">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C639">
         <v>5</v>
@@ -16888,7 +16847,7 @@
         </is>
       </c>
       <c r="B640">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C640">
         <v>5</v>
@@ -16913,7 +16872,7 @@
         </is>
       </c>
       <c r="B641">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C641">
         <v>5</v>
@@ -16938,7 +16897,7 @@
         </is>
       </c>
       <c r="B642">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C642">
         <v>5</v>
@@ -16963,7 +16922,7 @@
         </is>
       </c>
       <c r="B643">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C643">
         <v>5</v>
@@ -16988,7 +16947,7 @@
         </is>
       </c>
       <c r="B644">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C644">
         <v>5</v>
@@ -17013,7 +16972,7 @@
         </is>
       </c>
       <c r="B645">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C645">
         <v>5</v>
@@ -17038,7 +16997,7 @@
         </is>
       </c>
       <c r="B646">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C646">
         <v>5</v>
@@ -17063,7 +17022,7 @@
         </is>
       </c>
       <c r="B647">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C647">
         <v>5</v>
@@ -17088,7 +17047,7 @@
         </is>
       </c>
       <c r="B648">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C648">
         <v>5</v>
@@ -17113,7 +17072,7 @@
         </is>
       </c>
       <c r="B649">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C649">
         <v>5</v>
@@ -17138,7 +17097,7 @@
         </is>
       </c>
       <c r="B650">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C650">
         <v>5</v>
@@ -17163,7 +17122,7 @@
         </is>
       </c>
       <c r="B651">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C651">
         <v>5</v>
@@ -17188,7 +17147,7 @@
         </is>
       </c>
       <c r="B652">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C652">
         <v>5</v>
@@ -17213,7 +17172,7 @@
         </is>
       </c>
       <c r="B653">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C653">
         <v>5</v>
@@ -17238,7 +17197,7 @@
         </is>
       </c>
       <c r="B654">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C654">
         <v>5</v>
@@ -17263,7 +17222,7 @@
         </is>
       </c>
       <c r="B655">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C655">
         <v>5</v>
@@ -17288,7 +17247,7 @@
         </is>
       </c>
       <c r="B656">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C656">
         <v>5</v>
@@ -17313,7 +17272,7 @@
         </is>
       </c>
       <c r="B657">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C657">
         <v>5</v>
@@ -17338,7 +17297,7 @@
         </is>
       </c>
       <c r="B658">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C658">
         <v>5</v>
@@ -17363,7 +17322,7 @@
         </is>
       </c>
       <c r="B659">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C659">
         <v>5</v>
@@ -17388,7 +17347,7 @@
         </is>
       </c>
       <c r="B660">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C660">
         <v>5</v>
@@ -17413,7 +17372,7 @@
         </is>
       </c>
       <c r="B661">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C661">
         <v>5</v>
@@ -17438,7 +17397,7 @@
         </is>
       </c>
       <c r="B662">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C662">
         <v>5</v>
@@ -17463,7 +17422,7 @@
         </is>
       </c>
       <c r="B663">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C663">
         <v>5</v>
@@ -17488,7 +17447,7 @@
         </is>
       </c>
       <c r="B664">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C664">
         <v>5</v>
@@ -17513,7 +17472,7 @@
         </is>
       </c>
       <c r="B665">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C665">
         <v>5</v>
@@ -17538,7 +17497,7 @@
         </is>
       </c>
       <c r="B666">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C666">
         <v>5</v>
@@ -17563,7 +17522,7 @@
         </is>
       </c>
       <c r="B667">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C667">
         <v>5</v>
@@ -17588,7 +17547,7 @@
         </is>
       </c>
       <c r="B668">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C668">
         <v>5</v>
@@ -17613,7 +17572,7 @@
         </is>
       </c>
       <c r="B669">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C669">
         <v>5</v>
@@ -17638,7 +17597,7 @@
         </is>
       </c>
       <c r="B670">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C670">
         <v>5</v>
@@ -17663,7 +17622,7 @@
         </is>
       </c>
       <c r="B671">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C671">
         <v>5</v>
@@ -17688,7 +17647,7 @@
         </is>
       </c>
       <c r="B672">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C672">
         <v>5</v>
@@ -17713,7 +17672,7 @@
         </is>
       </c>
       <c r="B673">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C673">
         <v>5</v>
@@ -17738,7 +17697,7 @@
         </is>
       </c>
       <c r="B674">
-        <v>3</v>
+        <v>1998</v>
       </c>
       <c r="C674">
         <v>2</v>
@@ -17763,7 +17722,7 @@
         </is>
       </c>
       <c r="B675">
-        <v>4</v>
+        <v>1999</v>
       </c>
       <c r="C675">
         <v>2</v>
@@ -17788,7 +17747,7 @@
         </is>
       </c>
       <c r="B676">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="C676">
         <v>2</v>
@@ -17813,7 +17772,7 @@
         </is>
       </c>
       <c r="B677">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C677">
         <v>2</v>
@@ -17838,7 +17797,7 @@
         </is>
       </c>
       <c r="B678">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C678">
         <v>2</v>
@@ -17863,7 +17822,7 @@
         </is>
       </c>
       <c r="B679">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C679">
         <v>2</v>
@@ -17888,7 +17847,7 @@
         </is>
       </c>
       <c r="B680">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C680">
         <v>2</v>
@@ -17913,7 +17872,7 @@
         </is>
       </c>
       <c r="B681">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C681">
         <v>2</v>
@@ -17938,7 +17897,7 @@
         </is>
       </c>
       <c r="B682">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C682">
         <v>2</v>
@@ -17963,7 +17922,7 @@
         </is>
       </c>
       <c r="B683">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C683">
         <v>2</v>
@@ -17988,7 +17947,7 @@
         </is>
       </c>
       <c r="B684">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C684">
         <v>2</v>
@@ -18013,7 +17972,7 @@
         </is>
       </c>
       <c r="B685">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C685">
         <v>2</v>
@@ -18038,7 +17997,7 @@
         </is>
       </c>
       <c r="B686">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C686">
         <v>2</v>
@@ -18063,7 +18022,7 @@
         </is>
       </c>
       <c r="B687">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C687">
         <v>2</v>
@@ -18088,7 +18047,7 @@
         </is>
       </c>
       <c r="B688">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C688">
         <v>2</v>
@@ -18113,7 +18072,7 @@
         </is>
       </c>
       <c r="B689">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C689">
         <v>2</v>
@@ -18138,7 +18097,7 @@
         </is>
       </c>
       <c r="B690">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C690">
         <v>2</v>
@@ -18163,7 +18122,7 @@
         </is>
       </c>
       <c r="B691">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C691">
         <v>2</v>
@@ -18188,7 +18147,7 @@
         </is>
       </c>
       <c r="B692">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C692">
         <v>2</v>
@@ -18213,7 +18172,7 @@
         </is>
       </c>
       <c r="B693">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C693">
         <v>2</v>
@@ -18238,7 +18197,7 @@
         </is>
       </c>
       <c r="B694">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C694">
         <v>2</v>
@@ -18263,7 +18222,7 @@
         </is>
       </c>
       <c r="B695">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C695">
         <v>2</v>
@@ -18288,7 +18247,7 @@
         </is>
       </c>
       <c r="B696">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C696">
         <v>2</v>
@@ -18313,7 +18272,7 @@
         </is>
       </c>
       <c r="B697">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C697">
         <v>2</v>
@@ -18338,7 +18297,7 @@
         </is>
       </c>
       <c r="B698">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C698">
         <v>2</v>
@@ -18363,7 +18322,7 @@
         </is>
       </c>
       <c r="B699">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C699">
         <v>2</v>
@@ -18388,7 +18347,7 @@
         </is>
       </c>
       <c r="B700">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C700">
         <v>2</v>
@@ -18413,7 +18372,7 @@
         </is>
       </c>
       <c r="B701">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C701">
         <v>2</v>
@@ -18438,7 +18397,7 @@
         </is>
       </c>
       <c r="B702">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C702">
         <v>2</v>
@@ -18463,7 +18422,7 @@
         </is>
       </c>
       <c r="B703">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C703">
         <v>2</v>
@@ -18488,7 +18447,7 @@
         </is>
       </c>
       <c r="B704">
-        <v>4</v>
+        <v>1999</v>
       </c>
       <c r="C704">
         <v>3</v>
@@ -18513,7 +18472,7 @@
         </is>
       </c>
       <c r="B705">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="C705">
         <v>3</v>
@@ -18538,7 +18497,7 @@
         </is>
       </c>
       <c r="B706">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C706">
         <v>3</v>
@@ -18563,7 +18522,7 @@
         </is>
       </c>
       <c r="B707">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C707">
         <v>3</v>
@@ -18588,7 +18547,7 @@
         </is>
       </c>
       <c r="B708">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C708">
         <v>3</v>
@@ -18613,7 +18572,7 @@
         </is>
       </c>
       <c r="B709">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C709">
         <v>3</v>
@@ -18638,7 +18597,7 @@
         </is>
       </c>
       <c r="B710">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C710">
         <v>3</v>
@@ -18663,7 +18622,7 @@
         </is>
       </c>
       <c r="B711">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C711">
         <v>3</v>
@@ -18688,7 +18647,7 @@
         </is>
       </c>
       <c r="B712">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C712">
         <v>3</v>
@@ -18713,7 +18672,7 @@
         </is>
       </c>
       <c r="B713">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C713">
         <v>3</v>
@@ -18738,7 +18697,7 @@
         </is>
       </c>
       <c r="B714">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C714">
         <v>3</v>
@@ -18763,7 +18722,7 @@
         </is>
       </c>
       <c r="B715">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C715">
         <v>3</v>
@@ -18788,7 +18747,7 @@
         </is>
       </c>
       <c r="B716">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C716">
         <v>3</v>
@@ -18813,7 +18772,7 @@
         </is>
       </c>
       <c r="B717">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C717">
         <v>3</v>
@@ -18838,7 +18797,7 @@
         </is>
       </c>
       <c r="B718">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C718">
         <v>3</v>
@@ -18863,7 +18822,7 @@
         </is>
       </c>
       <c r="B719">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C719">
         <v>3</v>
@@ -18888,7 +18847,7 @@
         </is>
       </c>
       <c r="B720">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C720">
         <v>3</v>
@@ -18913,7 +18872,7 @@
         </is>
       </c>
       <c r="B721">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C721">
         <v>3</v>
@@ -18938,7 +18897,7 @@
         </is>
       </c>
       <c r="B722">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C722">
         <v>3</v>
@@ -18963,7 +18922,7 @@
         </is>
       </c>
       <c r="B723">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C723">
         <v>3</v>
@@ -18988,7 +18947,7 @@
         </is>
       </c>
       <c r="B724">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C724">
         <v>3</v>
@@ -19013,7 +18972,7 @@
         </is>
       </c>
       <c r="B725">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C725">
         <v>3</v>
@@ -19038,7 +18997,7 @@
         </is>
       </c>
       <c r="B726">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C726">
         <v>3</v>
@@ -19063,7 +19022,7 @@
         </is>
       </c>
       <c r="B727">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C727">
         <v>3</v>
@@ -19088,7 +19047,7 @@
         </is>
       </c>
       <c r="B728">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C728">
         <v>3</v>
@@ -19113,7 +19072,7 @@
         </is>
       </c>
       <c r="B729">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C729">
         <v>3</v>
@@ -19138,7 +19097,7 @@
         </is>
       </c>
       <c r="B730">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C730">
         <v>3</v>
@@ -19163,7 +19122,7 @@
         </is>
       </c>
       <c r="B731">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C731">
         <v>3</v>
@@ -19188,7 +19147,7 @@
         </is>
       </c>
       <c r="B732">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C732">
         <v>3</v>
@@ -19213,7 +19172,7 @@
         </is>
       </c>
       <c r="B733">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C733">
         <v>3</v>
@@ -19238,7 +19197,7 @@
         </is>
       </c>
       <c r="B734">
-        <v>6</v>
+        <v>2001</v>
       </c>
       <c r="C734">
         <v>5</v>
@@ -19263,7 +19222,7 @@
         </is>
       </c>
       <c r="B735">
-        <v>7</v>
+        <v>2002</v>
       </c>
       <c r="C735">
         <v>5</v>
@@ -19288,7 +19247,7 @@
         </is>
       </c>
       <c r="B736">
-        <v>8</v>
+        <v>2003</v>
       </c>
       <c r="C736">
         <v>5</v>
@@ -19313,7 +19272,7 @@
         </is>
       </c>
       <c r="B737">
-        <v>9</v>
+        <v>2004</v>
       </c>
       <c r="C737">
         <v>5</v>
@@ -19338,7 +19297,7 @@
         </is>
       </c>
       <c r="B738">
-        <v>10</v>
+        <v>2005</v>
       </c>
       <c r="C738">
         <v>5</v>
@@ -19363,7 +19322,7 @@
         </is>
       </c>
       <c r="B739">
-        <v>11</v>
+        <v>2006</v>
       </c>
       <c r="C739">
         <v>5</v>
@@ -19388,7 +19347,7 @@
         </is>
       </c>
       <c r="B740">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C740">
         <v>5</v>
@@ -19413,7 +19372,7 @@
         </is>
       </c>
       <c r="B741">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C741">
         <v>5</v>
@@ -19438,7 +19397,7 @@
         </is>
       </c>
       <c r="B742">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C742">
         <v>5</v>
@@ -19463,7 +19422,7 @@
         </is>
       </c>
       <c r="B743">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C743">
         <v>5</v>
@@ -19488,7 +19447,7 @@
         </is>
       </c>
       <c r="B744">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C744">
         <v>5</v>
@@ -19513,7 +19472,7 @@
         </is>
       </c>
       <c r="B745">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C745">
         <v>5</v>
@@ -19538,7 +19497,7 @@
         </is>
       </c>
       <c r="B746">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C746">
         <v>5</v>
@@ -19563,7 +19522,7 @@
         </is>
       </c>
       <c r="B747">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C747">
         <v>5</v>
@@ -19588,7 +19547,7 @@
         </is>
       </c>
       <c r="B748">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C748">
         <v>5</v>
@@ -19613,7 +19572,7 @@
         </is>
       </c>
       <c r="B749">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C749">
         <v>5</v>
@@ -19638,7 +19597,7 @@
         </is>
       </c>
       <c r="B750">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C750">
         <v>5</v>
@@ -19663,7 +19622,7 @@
         </is>
       </c>
       <c r="B751">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C751">
         <v>5</v>
@@ -19688,7 +19647,7 @@
         </is>
       </c>
       <c r="B752">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C752">
         <v>5</v>
@@ -19713,7 +19672,7 @@
         </is>
       </c>
       <c r="B753">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C753">
         <v>5</v>
@@ -19738,7 +19697,7 @@
         </is>
       </c>
       <c r="B754">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C754">
         <v>5</v>
@@ -19763,7 +19722,7 @@
         </is>
       </c>
       <c r="B755">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C755">
         <v>5</v>
@@ -19788,7 +19747,7 @@
         </is>
       </c>
       <c r="B756">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C756">
         <v>5</v>
@@ -19813,7 +19772,7 @@
         </is>
       </c>
       <c r="B757">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C757">
         <v>5</v>
@@ -19838,7 +19797,7 @@
         </is>
       </c>
       <c r="B758">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C758">
         <v>5</v>
@@ -19863,7 +19822,7 @@
         </is>
       </c>
       <c r="B759">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C759">
         <v>5</v>
@@ -19888,7 +19847,7 @@
         </is>
       </c>
       <c r="B760">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C760">
         <v>5</v>
@@ -19913,7 +19872,7 @@
         </is>
       </c>
       <c r="B761">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C761">
         <v>5</v>
@@ -19938,7 +19897,7 @@
         </is>
       </c>
       <c r="B762">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C762">
         <v>14</v>
@@ -19963,7 +19922,7 @@
         </is>
       </c>
       <c r="B763">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C763">
         <v>14</v>
@@ -19988,7 +19947,7 @@
         </is>
       </c>
       <c r="B764">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C764">
         <v>14</v>
@@ -20013,7 +19972,7 @@
         </is>
       </c>
       <c r="B765">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C765">
         <v>14</v>
@@ -20038,7 +19997,7 @@
         </is>
       </c>
       <c r="B766">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C766">
         <v>14</v>
@@ -20063,7 +20022,7 @@
         </is>
       </c>
       <c r="B767">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C767">
         <v>14</v>
@@ -20088,7 +20047,7 @@
         </is>
       </c>
       <c r="B768">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C768">
         <v>14</v>
@@ -20113,7 +20072,7 @@
         </is>
       </c>
       <c r="B769">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C769">
         <v>14</v>
@@ -20138,7 +20097,7 @@
         </is>
       </c>
       <c r="B770">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C770">
         <v>14</v>
@@ -20163,7 +20122,7 @@
         </is>
       </c>
       <c r="B771">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C771">
         <v>14</v>
@@ -20188,7 +20147,7 @@
         </is>
       </c>
       <c r="B772">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C772">
         <v>14</v>
@@ -20213,7 +20172,7 @@
         </is>
       </c>
       <c r="B773">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C773">
         <v>14</v>
@@ -20238,7 +20197,7 @@
         </is>
       </c>
       <c r="B774">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C774">
         <v>14</v>
@@ -20263,7 +20222,7 @@
         </is>
       </c>
       <c r="B775">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C775">
         <v>14</v>
@@ -20288,7 +20247,7 @@
         </is>
       </c>
       <c r="B776">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C776">
         <v>14</v>
@@ -20313,7 +20272,7 @@
         </is>
       </c>
       <c r="B777">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C777">
         <v>11</v>
@@ -20338,7 +20297,7 @@
         </is>
       </c>
       <c r="B778">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C778">
         <v>11</v>
@@ -20363,7 +20322,7 @@
         </is>
       </c>
       <c r="B779">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C779">
         <v>11</v>
@@ -20388,7 +20347,7 @@
         </is>
       </c>
       <c r="B780">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C780">
         <v>11</v>
@@ -20413,7 +20372,7 @@
         </is>
       </c>
       <c r="B781">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C781">
         <v>11</v>
@@ -20438,7 +20397,7 @@
         </is>
       </c>
       <c r="B782">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C782">
         <v>11</v>
@@ -20463,7 +20422,7 @@
         </is>
       </c>
       <c r="B783">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C783">
         <v>11</v>
@@ -20488,7 +20447,7 @@
         </is>
       </c>
       <c r="B784">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C784">
         <v>11</v>
@@ -20513,7 +20472,7 @@
         </is>
       </c>
       <c r="B785">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C785">
         <v>11</v>
@@ -20538,7 +20497,7 @@
         </is>
       </c>
       <c r="B786">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C786">
         <v>11</v>
@@ -20563,7 +20522,7 @@
         </is>
       </c>
       <c r="B787">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C787">
         <v>11</v>
@@ -20588,7 +20547,7 @@
         </is>
       </c>
       <c r="B788">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C788">
         <v>11</v>
@@ -20613,7 +20572,7 @@
         </is>
       </c>
       <c r="B789">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C789">
         <v>11</v>
@@ -20638,7 +20597,7 @@
         </is>
       </c>
       <c r="B790">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C790">
         <v>11</v>
@@ -20663,7 +20622,7 @@
         </is>
       </c>
       <c r="B791">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C791">
         <v>11</v>
@@ -20688,7 +20647,7 @@
         </is>
       </c>
       <c r="B792">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C792">
         <v>11</v>
@@ -20713,7 +20672,7 @@
         </is>
       </c>
       <c r="B793">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C793">
         <v>11</v>
@@ -20738,7 +20697,7 @@
         </is>
       </c>
       <c r="B794">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C794">
         <v>11</v>
@@ -20763,7 +20722,7 @@
         </is>
       </c>
       <c r="B795">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C795">
         <v>11</v>
@@ -20788,7 +20747,7 @@
         </is>
       </c>
       <c r="B796">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C796">
         <v>11</v>
@@ -20813,7 +20772,7 @@
         </is>
       </c>
       <c r="B797">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C797">
         <v>11</v>
@@ -20838,7 +20797,7 @@
         </is>
       </c>
       <c r="B798">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C798">
         <v>11</v>
@@ -20863,7 +20822,7 @@
         </is>
       </c>
       <c r="B799">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C799">
         <v>11</v>
@@ -20888,7 +20847,7 @@
         </is>
       </c>
       <c r="B800">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C800">
         <v>11</v>
@@ -20913,7 +20872,7 @@
         </is>
       </c>
       <c r="B801">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C801">
         <v>11</v>
@@ -20938,7 +20897,7 @@
         </is>
       </c>
       <c r="B802">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C802">
         <v>11</v>
@@ -20963,7 +20922,7 @@
         </is>
       </c>
       <c r="B803">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C803">
         <v>11</v>
@@ -20988,7 +20947,7 @@
         </is>
       </c>
       <c r="B804">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C804">
         <v>11</v>
@@ -21013,7 +20972,7 @@
         </is>
       </c>
       <c r="B805">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C805">
         <v>11</v>
@@ -21038,7 +20997,7 @@
         </is>
       </c>
       <c r="B806">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C806">
         <v>11</v>
@@ -21063,7 +21022,7 @@
         </is>
       </c>
       <c r="B807">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C807">
         <v>11</v>
@@ -21088,7 +21047,7 @@
         </is>
       </c>
       <c r="B808">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C808">
         <v>11</v>
@@ -21113,7 +21072,7 @@
         </is>
       </c>
       <c r="B809">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C809">
         <v>11</v>
@@ -21138,7 +21097,7 @@
         </is>
       </c>
       <c r="B810">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C810">
         <v>11</v>
@@ -21163,7 +21122,7 @@
         </is>
       </c>
       <c r="B811">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C811">
         <v>11</v>
@@ -21188,7 +21147,7 @@
         </is>
       </c>
       <c r="B812">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C812">
         <v>11</v>
@@ -21213,7 +21172,7 @@
         </is>
       </c>
       <c r="B813">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C813">
         <v>11</v>
@@ -21238,7 +21197,7 @@
         </is>
       </c>
       <c r="B814">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C814">
         <v>11</v>
@@ -21263,7 +21222,7 @@
         </is>
       </c>
       <c r="B815">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C815">
         <v>11</v>
@@ -21288,7 +21247,7 @@
         </is>
       </c>
       <c r="B816">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C816">
         <v>11</v>
@@ -21313,7 +21272,7 @@
         </is>
       </c>
       <c r="B817">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C817">
         <v>11</v>
@@ -21338,7 +21297,7 @@
         </is>
       </c>
       <c r="B818">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C818">
         <v>11</v>
@@ -21363,7 +21322,7 @@
         </is>
       </c>
       <c r="B819">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C819">
         <v>11</v>
@@ -21388,7 +21347,7 @@
         </is>
       </c>
       <c r="B820">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C820">
         <v>11</v>
@@ -21413,7 +21372,7 @@
         </is>
       </c>
       <c r="B821">
-        <v>12</v>
+        <v>2007</v>
       </c>
       <c r="C821">
         <v>11</v>
@@ -21438,7 +21397,7 @@
         </is>
       </c>
       <c r="B822">
-        <v>13</v>
+        <v>2008</v>
       </c>
       <c r="C822">
         <v>11</v>
@@ -21463,7 +21422,7 @@
         </is>
       </c>
       <c r="B823">
-        <v>14</v>
+        <v>2009</v>
       </c>
       <c r="C823">
         <v>11</v>
@@ -21488,7 +21447,7 @@
         </is>
       </c>
       <c r="B824">
-        <v>15</v>
+        <v>2010</v>
       </c>
       <c r="C824">
         <v>11</v>
@@ -21513,7 +21472,7 @@
         </is>
       </c>
       <c r="B825">
-        <v>16</v>
+        <v>2011</v>
       </c>
       <c r="C825">
         <v>11</v>
@@ -21538,7 +21497,7 @@
         </is>
       </c>
       <c r="B826">
-        <v>17</v>
+        <v>2012</v>
       </c>
       <c r="C826">
         <v>11</v>
@@ -21563,7 +21522,7 @@
         </is>
       </c>
       <c r="B827">
-        <v>18</v>
+        <v>2013</v>
       </c>
       <c r="C827">
         <v>11</v>
@@ -21588,7 +21547,7 @@
         </is>
       </c>
       <c r="B828">
-        <v>19</v>
+        <v>2014</v>
       </c>
       <c r="C828">
         <v>11</v>
@@ -21613,7 +21572,7 @@
         </is>
       </c>
       <c r="B829">
-        <v>20</v>
+        <v>2015</v>
       </c>
       <c r="C829">
         <v>11</v>
@@ -21638,7 +21597,7 @@
         </is>
       </c>
       <c r="B830">
-        <v>21</v>
+        <v>2016</v>
       </c>
       <c r="C830">
         <v>11</v>
@@ -21663,7 +21622,7 @@
         </is>
       </c>
       <c r="B831">
-        <v>22</v>
+        <v>2017</v>
       </c>
       <c r="C831">
         <v>11</v>
@@ -21688,7 +21647,7 @@
         </is>
       </c>
       <c r="B832">
-        <v>23</v>
+        <v>2018</v>
       </c>
       <c r="C832">
         <v>11</v>
@@ -21713,7 +21672,7 @@
         </is>
       </c>
       <c r="B833">
-        <v>24</v>
+        <v>2019</v>
       </c>
       <c r="C833">
         <v>11</v>
@@ -21738,7 +21697,7 @@
         </is>
       </c>
       <c r="B834">
-        <v>25</v>
+        <v>2020</v>
       </c>
       <c r="C834">
         <v>11</v>
@@ -21763,7 +21722,7 @@
         </is>
       </c>
       <c r="B835">
-        <v>26</v>
+        <v>2021</v>
       </c>
       <c r="C835">
         <v>11</v>
@@ -21788,7 +21747,7 @@
         </is>
       </c>
       <c r="B836">
-        <v>27</v>
+        <v>2022</v>
       </c>
       <c r="C836">
         <v>11</v>
@@ -21813,7 +21772,7 @@
         </is>
       </c>
       <c r="B837">
-        <v>28</v>
+        <v>2023</v>
       </c>
       <c r="C837">
         <v>11</v>
@@ -21838,7 +21797,7 @@
         </is>
       </c>
       <c r="B838">
-        <v>29</v>
+        <v>2024</v>
       </c>
       <c r="C838">
         <v>11</v>
@@ -21863,7 +21822,7 @@
         </is>
       </c>
       <c r="B839">
-        <v>30</v>
+        <v>2025</v>
       </c>
       <c r="C839">
         <v>11</v>
@@ -21888,7 +21847,7 @@
         </is>
       </c>
       <c r="B840">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C840">
         <v>11</v>
@@ -21913,7 +21872,7 @@
         </is>
       </c>
       <c r="B841">
-        <v>32</v>
+        <v>2027</v>
       </c>
       <c r="C841">
         <v>11</v>
@@ -21938,7 +21897,7 @@
         </is>
       </c>
       <c r="B842">
-        <v>33</v>
+        <v>2028</v>
       </c>
       <c r="C842">
         <v>11</v>
@@ -21959,8 +21918,8 @@
   </sheetData>
   <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>
@@ -22384,7 +22343,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>31</v>
+        <v>2026</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -22428,8 +22387,8 @@
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
-      <formula1>"1,2"</formula1>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E842">
+      <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="1" gridLinesSet="1"/>

--- a/tests/testthat/fixtures/example.xlsx
+++ b/tests/testthat/fixtures/example.xlsx
@@ -556,7 +556,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Observation Year  timing of the observation</t>
+          <t xml:space="preserve">  Observation Year  calendar year of the observation (1000-9999)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Target Year       timing of the target snapshot to predict</t>
+          <t xml:space="preserve">  Target Year       calendar year of the target snapshot (1000-9999)</t>
         </is>
       </c>
     </row>
